--- a/indicadores/ARG-ISS_out.xlsx
+++ b/indicadores/ARG-ISS_out.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/06/2026</t>
+    <t xml:space="preserve">01/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">ysonder</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1269,7 +1269,7 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>0.485729310418434</v>
+        <v>0.47639916148808</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -1327,7 +1327,7 @@
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15" t="n">
-        <v>0.235932962999567</v>
+        <v>0.226956161066546</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -1397,7 +1397,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.207073117055489</v>
+        <v>0.29126478520266</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1427,7 +1427,7 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>0.0360933322607553</v>
+        <v>0.04488494215352</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -1672,10 +1672,10 @@
         <v>787.328080192179</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>865.177476089026</v>
+        <v>865.177355929776</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>805.036332099064</v>
+        <v>805.036332109313</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>786.96355327574</v>
@@ -1696,7 +1696,7 @@
         <v>1.01759504833838</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.92603099128633</v>
+        <v>0.926031119897173</v>
       </c>
     </row>
     <row r="3">
@@ -1725,10 +1725,10 @@
         <v>830.084542665155</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>887.244121486426</v>
+        <v>887.244021708285</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>835.542348213706</v>
+        <v>835.542348221994</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>829.616360912497</v>
@@ -1753,7 +1753,7 @@
         <v>0.998837920155702</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.934489052190068</v>
+        <v>0.934489157281315</v>
       </c>
     </row>
     <row r="4">
@@ -1782,10 +1782,10 @@
         <v>863.981477130223</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>909.261883182068</v>
+        <v>909.261803860136</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>865.958000434232</v>
+        <v>865.958000440507</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>870.283397495507</v>
@@ -1810,7 +1810,7 @@
         <v>1.00015644125182</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.950349569752094</v>
+        <v>0.950349652658429</v>
       </c>
     </row>
     <row r="5">
@@ -1839,10 +1839,10 @@
         <v>896.640668661375</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>931.145860123834</v>
+        <v>931.145801470671</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>896.163294930019</v>
+        <v>896.163294934137</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>886.283401992716</v>
@@ -1867,7 +1867,7 @@
         <v>0.999177149121885</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.962150942689759</v>
+        <v>0.962151003295945</v>
       </c>
     </row>
     <row r="6">
@@ -1896,10 +1896,10 @@
         <v>933.341254450802</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>952.786789706053</v>
+        <v>952.786752121258</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>926.05986485575</v>
+        <v>926.059864857443</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>940.761266918315</v>
@@ -1926,7 +1926,7 @@
         <v>0.997387529720641</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.977031732828962</v>
+        <v>0.977031771370155</v>
       </c>
     </row>
     <row r="7">
@@ -1955,10 +1955,10 @@
         <v>954.723469186352</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>974.047370286722</v>
+        <v>974.047354393588</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>955.499943901422</v>
+        <v>955.499943900278</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>955.805776822852</v>
@@ -1985,7 +1985,7 @@
         <v>0.996867722125414</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.977091093328775</v>
+        <v>0.977091109271573</v>
       </c>
     </row>
     <row r="8">
@@ -2014,10 +2014,10 @@
         <v>954.899709050316</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>994.782784272096</v>
+        <v>994.782790941101</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>984.409272767346</v>
+        <v>984.409272762799</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>954.559219385868</v>
@@ -2044,7 +2044,7 @@
         <v>1.00529617422868</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.964991593599786</v>
+        <v>0.964991587130501</v>
       </c>
     </row>
     <row r="9">
@@ -2073,10 +2073,10 @@
         <v>985.343367101597</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1014.83681307252</v>
+        <v>1014.83684343126</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1012.71512131844</v>
+        <v>1012.71512130978</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>974.903881526865</v>
@@ -2103,7 +2103,7 @@
         <v>1.00331823902238</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.974159548784632</v>
+        <v>0.974159519642749</v>
       </c>
     </row>
     <row r="10">
@@ -2132,10 +2132,10 @@
         <v>1034.8064104686</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1034.02809837027</v>
+        <v>1034.02815379929</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1040.19550915271</v>
+        <v>1040.19550913909</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>1050.08490521143</v>
@@ -2162,7 +2162,7 @@
         <v>1.00169588032332</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.00244985598775</v>
+        <v>1.00244980225147</v>
       </c>
     </row>
     <row r="11">
@@ -2191,10 +2191,10 @@
         <v>1085.56532501182</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1052.15032376542</v>
+        <v>1052.15040587925</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1066.43939966921</v>
+        <v>1066.43939964972</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>1071.1715812445</v>
@@ -2221,7 +2221,7 @@
         <v>0.997116367809172</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.02878355824819</v>
+        <v>1.02878347795799</v>
       </c>
     </row>
     <row r="12">
@@ -2250,10 +2250,10 @@
         <v>1129.95330183585</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1069.00720836231</v>
+        <v>1069.00731897482</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1091.08520324729</v>
+        <v>1091.085203221</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>1137.31174788104</v>
@@ -2280,7 +2280,7 @@
         <v>0.995045377382429</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.05177476901419</v>
+        <v>1.05177466018477</v>
       </c>
     </row>
     <row r="13">
@@ -2309,10 +2309,10 @@
         <v>1146.69389986817</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1084.41435955123</v>
+        <v>1084.41450062427</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1113.79499117417</v>
+        <v>1113.79499114022</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>1151.62416159251</v>
@@ -2339,7 +2339,7 @@
         <v>0.993726982748443</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.05079821123321</v>
+        <v>1.05079807453336</v>
       </c>
     </row>
     <row r="14">
@@ -2368,10 +2368,10 @@
         <v>1120.02758790005</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1098.23007505963</v>
+        <v>1098.23024863396</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>1134.46196746023</v>
+        <v>1134.461967418</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>1117.4426059421</v>
@@ -2398,7 +2398,7 @@
         <v>1.00259934569772</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.0224987935529</v>
+        <v>1.02249863194786</v>
       </c>
     </row>
     <row r="15">
@@ -2427,10 +2427,10 @@
         <v>1110.73830140415</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>1110.35465874126</v>
+        <v>1110.35486684834</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>1153.16848196797</v>
+        <v>1153.1684819172</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>1105.24633369124</v>
@@ -2457,7 +2457,7 @@
         <v>1.00794329161176</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.00829154975198</v>
+        <v>1.00829136077401</v>
       </c>
     </row>
     <row r="16">
@@ -2486,10 +2486,10 @@
         <v>1154.73178039847</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1120.70042228166</v>
+        <v>1120.70066683518</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>1169.91178775227</v>
+        <v>1169.91178769331</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>1150.30960522166</v>
@@ -2516,7 +2516,7 @@
         <v>0.999892308216576</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.03025518891388</v>
+        <v>1.03025496409691</v>
       </c>
     </row>
     <row r="17">
@@ -2545,10 +2545,10 @@
         <v>1193.30186694775</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1129.17648466324</v>
+        <v>1129.17676732903</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>1184.44952712664</v>
+        <v>1184.4495270607</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>1222.59157449259</v>
@@ -2575,7 +2575,7 @@
         <v>0.999168663138357</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05591096459495</v>
+        <v>1.05591070026971</v>
       </c>
     </row>
     <row r="18">
@@ -2604,10 +2604,10 @@
         <v>1221.09939587365</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>1135.71047060771</v>
+        <v>1135.71079265093</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>1196.44133149193</v>
+        <v>1196.44133142136</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>1189.57359278715</v>
@@ -2634,7 +2634,7 @@
         <v>0.995597712692566</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.07045219443258</v>
+        <v>1.07045189089415</v>
       </c>
     </row>
     <row r="19">
@@ -2663,10 +2663,10 @@
         <v>1239.1760989924</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>1140.28212213198</v>
+        <v>1140.28248424044</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1205.68740539818</v>
+        <v>1205.68740532678</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>1262.72809438243</v>
@@ -2693,7 +2693,7 @@
         <v>0.996329384383448</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.08273868009384</v>
+        <v>1.08273833625901</v>
       </c>
     </row>
     <row r="20">
@@ -2722,10 +2722,10 @@
         <v>1224.46749876132</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>1142.90748808718</v>
+        <v>1142.90789017004</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1211.9747537646</v>
+        <v>1211.97475369803</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>1219.25264530937</v>
@@ -2752,7 +2752,7 @@
         <v>0.997400492664333</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06857685267248</v>
+        <v>1.06857647673979</v>
       </c>
     </row>
     <row r="21">
@@ -2781,10 +2781,10 @@
         <v>1193.01539789224</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1143.67914605707</v>
+        <v>1143.67958701855</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1215.37558495534</v>
+        <v>1215.37558490144</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>1183.90456106284</v>
@@ -2811,7 +2811,7 @@
         <v>1.00441927671621</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.04774810941812</v>
+        <v>1.04774770544435</v>
       </c>
     </row>
     <row r="22">
@@ -2840,10 +2840,10 @@
         <v>1201.26749695841</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1142.73738934871</v>
+        <v>1142.73786683678</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>1215.99849679228</v>
+        <v>1215.99849676139</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>1206.08888481385</v>
@@ -2870,7 +2870,7 @@
         <v>1.00044579620416</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.05168784066275</v>
+        <v>1.05168740121954</v>
       </c>
     </row>
     <row r="23">
@@ -2899,10 +2899,10 @@
         <v>1208.18083055065</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1140.24765215349</v>
+        <v>1140.24816228427</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1213.79473197783</v>
+        <v>1213.79473198309</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>1211.12973910437</v>
@@ -2929,7 +2929,7 @@
         <v>0.997028383180021</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.05642890629768</v>
+        <v>1.05642843366644</v>
       </c>
     </row>
     <row r="24">
@@ -2958,10 +2958,10 @@
         <v>1186.16846425605</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>1136.4149633475</v>
+        <v>1136.41550040682</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>1208.6659851545</v>
+        <v>1208.66598521199</v>
       </c>
       <c r="K24" s="11" t="n">
         <v>1190.01395726945</v>
@@ -2988,7 +2988,7 @@
         <v>1.00825818212735</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.05240083775797</v>
+        <v>1.05240034040318</v>
       </c>
     </row>
     <row r="25">
@@ -3017,10 +3017,10 @@
         <v>1192.69858422713</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1131.48865311116</v>
+        <v>1131.48920923576</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1200.50062600045</v>
+        <v>1200.50062612915</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>1101.49479167473</v>
@@ -3047,7 +3047,7 @@
         <v>1.01097258422069</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06566297998394</v>
+        <v>1.0656624562128</v>
       </c>
     </row>
     <row r="26">
@@ -3070,16 +3070,16 @@
         <v>1.14252300854221</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.933234916931458</v>
+        <v>0.933234916931445</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>1226.88797227076</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>1125.75155099611</v>
+        <v>1125.75211583793</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>1189.0937640544</v>
+        <v>1189.09376427594</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>1249.22230759964</v>
@@ -3094,19 +3094,19 @@
         <v>1230.67449553696</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0204311096858622</v>
+        <v>0.020431109685862</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0240234694613477</v>
+        <v>0.0240234694613473</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0206412535246425</v>
+        <v>0.0206412535246423</v>
       </c>
       <c r="R26" s="18" t="n">
         <v>1.00308628281619</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.09320257604621</v>
+        <v>1.093202027536</v>
       </c>
     </row>
     <row r="27">
@@ -3135,10 +3135,10 @@
         <v>1243.43392363094</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>1119.52474276092</v>
+        <v>1119.52530313955</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>1174.2014986462</v>
+        <v>1174.2014989842</v>
       </c>
       <c r="K27" s="11" t="n">
         <v>1234.53709022847</v>
@@ -3153,19 +3153,19 @@
         <v>1236.72429918071</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00490380053692535</v>
+        <v>0.00490380053692778</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0266760504683272</v>
+        <v>0.0266760504683292</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0049158438447241</v>
+        <v>0.00491584384472654</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.994603955769006</v>
+        <v>0.994603955769008</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.10468688358844</v>
+        <v>1.10468633063719</v>
       </c>
     </row>
     <row r="28">
@@ -3185,46 +3185,46 @@
         <v>1143.39024827993</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.929516146892252</v>
+        <v>0.929516146892244</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1217.85697809373</v>
+        <v>1217.85697809375</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1113.20555141593</v>
+        <v>1113.20609096559</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1155.87311605468</v>
+        <v>1155.87311653361</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>1230.09186241977</v>
+        <v>1230.09186241978</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1230.09186241977</v>
+        <v>1230.09186241978</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>1224.47948183791</v>
+        <v>1224.47948183792</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>1224.47948183791</v>
+        <v>1224.47948183792</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0099503490661337</v>
+        <v>-0.00995034906612663</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0238430428946241</v>
+        <v>0.0238430428946335</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00990100813164896</v>
+        <v>-0.00990100813164196</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00543783372211</v>
+        <v>1.0054378337221</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.09995811670221</v>
+        <v>1.0999575835736</v>
       </c>
     </row>
     <row r="29">
@@ -3244,7 +3244,7 @@
         <v>1253.57935444932</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.04187363953197</v>
+        <v>1.04187363953195</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
@@ -3253,16 +3253,16 @@
         <v>1235.27197745032</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1107.26318268867</v>
+        <v>1107.26368150797</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1134.45958051657</v>
+        <v>1134.45958116009</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>1203.19711228365</v>
+        <v>1203.19711228367</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1203.19711228365</v>
+        <v>1203.19711228367</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>1231.80552991643</v>
@@ -3271,19 +3271,19 @@
         <v>1231.80552991643</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.00596516264775057</v>
+        <v>0.00596516264773688</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0215792597570197</v>
+        <v>0.0215792597570148</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0059829896598389</v>
+        <v>0.00598298965982513</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>0.997193777890889</v>
+        <v>0.997193777890884</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.11247763781447</v>
+        <v>1.11247713664631</v>
       </c>
     </row>
     <row r="30">
@@ -3303,46 +3303,46 @@
         <v>1449.81126794023</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.12324381688751</v>
+        <v>1.12324381688758</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1256.17646698708</v>
+        <v>1256.17646698698</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1102.23989625106</v>
+        <v>1102.24033056574</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1110.68295000041</v>
+        <v>1110.682950829</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>1290.73603267867</v>
+        <v>1290.73603267859</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1290.73603267867</v>
+        <v>1290.73603267859</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1244.35796950621</v>
+        <v>1244.35796950615</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1244.35796950621</v>
+        <v>1244.35796950615</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.010138706202673</v>
+        <v>0.010138706202629</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0111186784311101</v>
+        <v>0.0111186784310613</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0101902770241877</v>
+        <v>0.0101902770241433</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.990591690107666</v>
+        <v>0.990591690107697</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.1289357006025</v>
+        <v>1.12893525576901</v>
       </c>
     </row>
     <row r="31">
@@ -3362,46 +3362,46 @@
         <v>1073.94141993997</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.900381458603933</v>
+        <v>0.900381458604012</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1201.36291431589</v>
+        <v>1201.36291431591</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1098.73791048097</v>
+        <v>1098.73825233221</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1085.60897013361</v>
+        <v>1085.60897116128</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>1192.76270038384</v>
+        <v>1192.76270038374</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1192.76270038384</v>
+        <v>1192.76270038374</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>1189.06524911799</v>
+        <v>1189.065249118</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>1189.06524911799</v>
+        <v>1189.065249118</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0454522162508088</v>
+        <v>-0.0454522162507446</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.038536519492902</v>
+        <v>-0.0385365194928889</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.044434738028129</v>
+        <v>-0.0444347380280676</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.989763571813845</v>
+        <v>0.989763571813844</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.08221008647774</v>
+        <v>1.08220974976894</v>
       </c>
     </row>
     <row r="32">
@@ -3421,46 +3421,46 @@
         <v>1006.17899473794</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.931647594300093</v>
+        <v>0.931647594299779</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1092.52573847687</v>
+        <v>1092.5257384771</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1097.47725384158</v>
+        <v>1097.47747081451</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1061.20365195693</v>
+        <v>1061.20365318717</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1079.99956302559</v>
+        <v>1079.99956302595</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1079.99956302559</v>
+        <v>1079.99956302595</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1089.09872865009</v>
+        <v>1089.09872865026</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1089.09872865009</v>
+        <v>1089.09872865026</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.0878169937510056</v>
+        <v>-0.0878169937508665</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.110561879717752</v>
+        <v>-0.110561879717622</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.0840715179777086</v>
+        <v>-0.0840715179775813</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.996863222800084</v>
+        <v>0.996863222800028</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.99236565025639</v>
+        <v>0.992365454064376</v>
       </c>
     </row>
     <row r="33">
@@ -3480,46 +3480,46 @@
         <v>1097.12674299929</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.0592612194256</v>
+        <v>1.05926121942552</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0.402706876595951</v>
+        <v>0.402706876595884</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>981.981179758366</v>
+        <v>981.981179758405</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1099.23672028974</v>
+        <v>1099.23677529978</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1039.96877516241</v>
+        <v>1039.96877658297</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1035.74710645427</v>
+        <v>1035.74710645435</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1003.63308816536</v>
+        <v>1003.63308816541</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>984.819445896608</v>
+        <v>984.819445896618</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>984.819445896608</v>
+        <v>984.819445896618</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.100647458029386</v>
+        <v>-0.100647458029531</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.200507367454813</v>
+        <v>-0.200507367454801</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.095748236601779</v>
+        <v>-0.0957482366019097</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00289034677726</v>
+        <v>1.00289034677723</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.895912070365544</v>
+        <v>0.895912025530663</v>
       </c>
     </row>
     <row r="34">
@@ -3539,46 +3539,46 @@
         <v>925.043759968322</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.10386259850482</v>
+        <v>1.10386259850541</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.596425102218408</v>
+        <v>0.59642510221825</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>872.710570151928</v>
+        <v>872.71057015152</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1104.78418022554</v>
+        <v>1104.78403138281</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1024.50009899743</v>
+        <v>1024.5001005742</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>838.006252971422</v>
+        <v>838.006252970974</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>852.012044230125</v>
+        <v>852.012044229699</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>885.474395052341</v>
+        <v>885.474395052086</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>885.474395052341</v>
+        <v>885.474395052086</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.106334779714469</v>
+        <v>-0.106334779714767</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.288408627781185</v>
+        <v>-0.288408627781356</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.100876410653956</v>
+        <v>-0.100876410654224</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.01462549593984</v>
+        <v>1.01462549594002</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.801490834953462</v>
+        <v>0.801490942934593</v>
       </c>
     </row>
     <row r="35">
@@ -3598,46 +3598,46 @@
         <v>751.640121231456</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.900987434800015</v>
+        <v>0.900987434800251</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>841.773184952378</v>
+        <v>841.773184952478</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1114.827751779</v>
+        <v>1114.82735235393</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1017.21170427437</v>
+        <v>1017.21170594431</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>834.240403583754</v>
+        <v>834.240403583535</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>834.240403583754</v>
+        <v>834.240403583535</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>855.495684592805</v>
+        <v>855.49568459289</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>855.495684592805</v>
+        <v>855.49568459289</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0344424919876476</v>
+        <v>-0.0344424919872608</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.280530916846332</v>
+        <v>-0.280530916846272</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0338561008957957</v>
+        <v>-0.033856100895422</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.01630189685979</v>
+        <v>1.01630189685977</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.767379250496444</v>
+        <v>0.767379525436414</v>
       </c>
     </row>
     <row r="36">
@@ -3657,46 +3657,46 @@
         <v>839.434712132987</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.931163759308572</v>
+        <v>0.931163759307332</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>883.713693465474</v>
+        <v>883.713693466151</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1129.91757049514</v>
+        <v>1129.91686901148</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1019.65523153179</v>
+        <v>1019.65523319499</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>901.489886973589</v>
+        <v>901.489886974789</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>901.489886973589</v>
+        <v>901.489886974789</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>886.168604021672</v>
+        <v>886.168604022196</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>886.168604021672</v>
+        <v>886.168604022196</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0352261814840344</v>
+        <v>0.0352261814845276</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.186328492807946</v>
+        <v>-0.186328492807591</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0358539732944017</v>
+        <v>0.0358539732949126</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00277794785161</v>
+        <v>1.00277794785143</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.784277213808919</v>
+        <v>0.78427770071038</v>
       </c>
     </row>
     <row r="37">
@@ -3716,46 +3716,46 @@
         <v>979.295252197054</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.07916764348981</v>
+        <v>1.07916764348991</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>907.529823709802</v>
+        <v>907.529823709948</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1150.42840482636</v>
+        <v>1150.42734531086</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1032.46746480479</v>
+        <v>1032.46746631615</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>907.454238555755</v>
+        <v>907.454238555671</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>907.454238555755</v>
+        <v>907.454238555671</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>915.610061325828</v>
+        <v>915.610061325877</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>915.610061325828</v>
+        <v>915.610061325877</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0326833463032188</v>
+        <v>0.03268334630268</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0702762164771935</v>
+        <v>-0.0702762164771535</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0332233134536064</v>
+        <v>0.0332233134530497</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00890355050041</v>
+        <v>1.0089035505003</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.795886173780653</v>
+        <v>0.79588690677243</v>
       </c>
     </row>
     <row r="38">
@@ -3775,46 +3775,46 @@
         <v>1025.67860484186</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.08417885635369</v>
+        <v>1.08417885635465</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>970.103942617978</v>
+        <v>970.103942617034</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1176.59225592284</v>
+        <v>1176.59077834364</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1055.69436140569</v>
+        <v>1055.69436256659</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>946.041881218215</v>
+        <v>946.041881217378</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>946.041881218215</v>
+        <v>946.041881217378</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>977.417460257216</v>
+        <v>977.417460256541</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>977.417460257216</v>
+        <v>977.417460256541</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0653232718629414</v>
+        <v>0.0653232718621984</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>0.103834809587509</v>
+        <v>0.103834809587066</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0675040626376346</v>
+        <v>0.0675040626368415</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00753890105786</v>
+        <v>1.00753890105815</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.830718930315067</v>
+        <v>0.830719973542976</v>
       </c>
     </row>
     <row r="39">
@@ -3834,46 +3834,46 @@
         <v>1000.69836644118</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.901422993514098</v>
+        <v>0.901422993514859</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1081.07321789027</v>
+        <v>1081.07321788959</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1208.48926608088</v>
+        <v>1208.48730700973</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1088.75681251553</v>
+        <v>1088.75681306632</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1110.13184003668</v>
+        <v>1110.13184003574</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1110.13184003668</v>
+        <v>1110.13184003574</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1082.80158534066</v>
+        <v>1082.80158534029</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1082.80158534066</v>
+        <v>1082.80158534029</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.102393173191516</v>
+        <v>0.102393173191862</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.265700815143268</v>
+        <v>0.265700815142708</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.107818950825488</v>
+        <v>0.107818950825871</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>1.00159875152005</v>
+        <v>1.00159875152034</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.895996030525103</v>
+        <v>0.895997483018309</v>
       </c>
     </row>
     <row r="40">
@@ -3893,46 +3893,46 @@
         <v>1086.52423367125</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.93271826430141</v>
+        <v>0.932718264300431</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1189.5626017281</v>
+        <v>1189.56260173006</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1246.05548361255</v>
+        <v>1246.05297714828</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1130.52744691446</v>
+        <v>1130.52744652858</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1164.90078007108</v>
+        <v>1164.9007800723</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1164.90078007108</v>
+        <v>1164.9007800723</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1177.80238132901</v>
+        <v>1177.80238133033</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1177.80238132901</v>
+        <v>1177.80238133033</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0840985705021562</v>
+        <v>0.0840985705036166</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.329095136054054</v>
+        <v>0.329095136054751</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0877361072190015</v>
+        <v>0.08773610722059</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.990113828072604</v>
+        <v>0.990113828072078</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.945224668418735</v>
+        <v>0.945226569760984</v>
       </c>
     </row>
     <row r="41">
@@ -3952,46 +3952,46 @@
         <v>1387.01112527143</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.09103844384847</v>
+        <v>1.09103844384525</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1246.60401004007</v>
+        <v>1246.6040100408</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1289.16548343866</v>
+        <v>1289.16236243162</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1179.98576852019</v>
+        <v>1179.98576680148</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1271.27612513723</v>
+        <v>1271.27612514098</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1271.27612513723</v>
+        <v>1271.27612514098</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1240.44195146927</v>
+        <v>1240.44195147009</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1240.44195146927</v>
+        <v>1240.44195147009</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0518174152210539</v>
+        <v>0.0518174152206044</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.354770992438715</v>
+        <v>0.354770992439547</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0531834296935019</v>
+        <v>0.0531834296930285</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.995056923833731</v>
+        <v>0.995056923833812</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.962205370376944</v>
+        <v>0.962207699835705</v>
       </c>
     </row>
     <row r="42">
@@ -4011,46 +4011,46 @@
         <v>1344.70366909301</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.07206236849373</v>
+        <v>1.07206236849836</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1265.64713679668</v>
+        <v>1265.64713679574</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1337.6431187903</v>
+        <v>1337.63931640889</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1236.28314791626</v>
+        <v>1236.28314440083</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1254.31477553153</v>
+        <v>1254.31477552611</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1254.31477553153</v>
+        <v>1254.31477552611</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1263.74750453036</v>
+        <v>1263.74750452927</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1263.74750453036</v>
+        <v>1263.74750452927</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0186137881037608</v>
+        <v>0.0186137881022295</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.292945497615516</v>
+        <v>0.29294549761529</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0187881045408771</v>
+        <v>0.018788104539317</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.998499082239361</v>
+        <v>0.998499082239239</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.944756853885832</v>
+        <v>0.94475953945642</v>
       </c>
     </row>
     <row r="43">
@@ -4070,46 +4070,46 @@
         <v>1151.18082419785</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.90282719844507</v>
+        <v>0.90282719844315</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1278.88937794833</v>
+        <v>1278.88937794642</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1391.30106204964</v>
+        <v>1391.29651373093</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1299.02740746925</v>
+        <v>1299.02740163417</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1275.08434192115</v>
+        <v>1275.08434192386</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1275.08434192115</v>
+        <v>1275.08434192386</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1286.19998166019</v>
+        <v>1286.1999816592</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1286.19998166019</v>
+        <v>1286.1999816592</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0176106037636303</v>
+        <v>0.0176106037637276</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.187844568269202</v>
+        <v>0.187844568268699</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0177665847404935</v>
+        <v>0.0177665847405926</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00571636909174</v>
+        <v>1.00571636909247</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.924458420067171</v>
+        <v>0.924461442234263</v>
       </c>
     </row>
     <row r="44">
@@ -4129,46 +4129,46 @@
         <v>1247.82293557512</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.930991274112749</v>
+        <v>0.930991274115495</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1332.7914763159</v>
+        <v>1332.79147631684</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1449.89990538428</v>
+        <v>1449.89455121052</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1367.91652768384</v>
+        <v>1367.91651896462</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1340.31646726691</v>
+        <v>1340.31646726296</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1340.31646726691</v>
+        <v>1340.31646726296</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1340.15977603456</v>
+        <v>1340.15977603461</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1340.15977603456</v>
+        <v>1340.15977603461</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.041096722241766</v>
+        <v>0.0410967222425701</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.137847738533474</v>
+        <v>0.137847738532246</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0419528806902369</v>
+        <v>0.0419528806910747</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00552847151981</v>
+        <v>1.00552847151914</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.924311927366711</v>
+        <v>0.924315340667847</v>
       </c>
     </row>
     <row r="45">
@@ -4188,46 +4188,46 @@
         <v>1544.43982105477</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.09930658818332</v>
+        <v>1.0993065881791</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1414.47952432983</v>
+        <v>1414.47952432825</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1513.12760551179</v>
+        <v>1513.12139305307</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1442.52877373698</v>
+        <v>1442.52876155679</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1404.92182768327</v>
+        <v>1404.92182768866</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1404.92182768327</v>
+        <v>1404.92182768866</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1419.11360800321</v>
+        <v>1419.11360800366</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1419.11360800321</v>
+        <v>1419.11360800366</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0572436142893991</v>
+        <v>0.0572436142896836</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.144038708399301</v>
+        <v>0.144038708398906</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0589137454955302</v>
+        <v>0.0589137454958315</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1.00327617586092</v>
+        <v>1.00327617586236</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.937867766627137</v>
+        <v>0.937871617253571</v>
       </c>
     </row>
     <row r="46">
@@ -4247,46 +4247,46 @@
         <v>1628.14312336858</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.06672947239816</v>
+        <v>1.06672947240166</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1523.12820120016</v>
+        <v>1523.12820120985</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1580.60362950085</v>
+        <v>1580.59651716152</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1522.30441050352</v>
+        <v>1522.30439431675</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1526.29430937938</v>
+        <v>1526.29430937437</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1526.29430937938</v>
+        <v>1526.29430937437</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1522.29287981214</v>
+        <v>1522.29287981697</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1522.29287981214</v>
+        <v>1522.29287981697</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0701852148245667</v>
+        <v>0.0701852148274183</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.204586259798681</v>
+        <v>0.204586259803544</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0727068440659349</v>
+        <v>0.0727068440689937</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.999451575128502</v>
+        <v>0.999451575125315</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>0.963108556376576</v>
+        <v>0.963112890157917</v>
       </c>
     </row>
     <row r="47">
@@ -4306,46 +4306,46 @@
         <v>1470.67718086851</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.901337419503962</v>
+        <v>0.901337419490735</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1623.94071432043</v>
+        <v>1623.94071431596</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1651.87981580907</v>
+        <v>1651.87177671046</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1606.49566812803</v>
+        <v>1606.49564748125</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1631.66107280654</v>
+        <v>1631.66107283048</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1631.66107280654</v>
+        <v>1631.66107283048</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1620.24627786711</v>
+        <v>1620.2462778656</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1620.24627786711</v>
+        <v>1620.2462778656</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.0623604892492243</v>
+        <v>0.0623604892451224</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.259715674832887</v>
+        <v>0.259715674832684</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0643459608554782</v>
+        <v>0.0643459608511123</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.997725017655667</v>
+        <v>0.997725017657487</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.980849976106484</v>
+        <v>0.980854749569099</v>
       </c>
     </row>
     <row r="48">
@@ -4365,46 +4365,46 @@
         <v>1577.11367430347</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.932448208889858</v>
+        <v>0.932448208916817</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1702.59001311088</v>
+        <v>1702.5900130976</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1726.47405956893</v>
+        <v>1726.4650859946</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1694.37472624948</v>
+        <v>1694.37470086233</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1691.36865647597</v>
+        <v>1691.36865642707</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1691.36865647597</v>
+        <v>1691.36865642707</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1698.82647862896</v>
+        <v>1698.82647861606</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1698.82647862896</v>
+        <v>1698.82647861606</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0473595449372871</v>
+        <v>0.0473595449306238</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.26762980728736</v>
+        <v>0.267629807277689</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0484989237965081</v>
+        <v>0.0484989237895217</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.997789523929462</v>
+        <v>0.997789523929669</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.983986101159915</v>
+        <v>0.983991215575254</v>
       </c>
     </row>
     <row r="49">
@@ -4424,46 +4424,46 @@
         <v>1958.50082068495</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.09972066997297</v>
+        <v>1.09972066995922</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1769.14027929936</v>
+        <v>1769.1402792893</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1803.89161919855</v>
+        <v>1803.88172761874</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1785.33959153023</v>
+        <v>1785.33956139875</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1780.90752875736</v>
+        <v>1780.90752877963</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1780.90752875736</v>
+        <v>1780.90752877963</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1769.03192041248</v>
+        <v>1769.03192041095</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1769.03192041248</v>
+        <v>1769.03192041095</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0404947533387762</v>
+        <v>0.0404947533455001</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.246575263908317</v>
+        <v>0.246575263906834</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0413258462042463</v>
+        <v>0.041325846211248</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.99993875053994</v>
+        <v>0.999938750544758</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.980675280923166</v>
+        <v>0.980680658452149</v>
       </c>
     </row>
     <row r="50">
@@ -4483,46 +4483,46 @@
         <v>1945.13754028478</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.0670308988062</v>
+        <v>1.06703089880724</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>1826.98871211719</v>
+        <v>1826.98871216181</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1883.61581223912</v>
+        <v>1883.60504891919</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>1878.77324028376</v>
+        <v>1878.77320580713</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>1822.94396765924</v>
+        <v>1822.94396765746</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1822.94396765924</v>
+        <v>1822.94396765746</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1831.79961149492</v>
+        <v>1831.79961151962</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>1831.79961149492</v>
+        <v>1831.79961151962</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0348664185567485</v>
+        <v>0.0348664185711022</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.203316152750428</v>
+        <v>0.203316152762837</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0354813784636507</v>
+        <v>0.0354813784785137</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00263323979279</v>
+        <v>1.00263323978182</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.972491099083203</v>
+        <v>0.972496656117321</v>
       </c>
     </row>
     <row r="51">
@@ -4542,46 +4542,46 @@
         <v>1712.91881357271</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.9013450462263</v>
+        <v>0.901345046188311</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>1910.54382473005</v>
+        <v>1910.543824718</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1965.11559117529</v>
+        <v>1965.104038358</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>1974.03648850969</v>
+        <v>1974.03645064096</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1900.40298190383</v>
+        <v>1900.40298198393</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1900.40298190383</v>
+        <v>1900.40298198393</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>1916.21848607515</v>
+        <v>1916.21848607401</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>1916.21848607515</v>
+        <v>1916.21848607401</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0450548275482921</v>
+        <v>0.0450548275342141</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.182671123674889</v>
+        <v>0.182671123675287</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.046085212623961</v>
+        <v>0.0460852126092341</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00297018119744</v>
+        <v>1.00297018120317</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.975117440765456</v>
+        <v>0.97512317346575</v>
       </c>
     </row>
     <row r="52">
@@ -4601,46 +4601,46 @@
         <v>1898.85436922996</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.930298383288222</v>
+        <v>0.930298383362494</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2021.33452849083</v>
+        <v>2021.33452842399</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2047.82198858888</v>
+        <v>2047.80977122141</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2070.21100584454</v>
+        <v>2070.21096626301</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2041.1240128337</v>
+        <v>2041.12401267074</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2041.1240128337</v>
+        <v>2041.12401267074</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2029.37222200378</v>
+        <v>2029.3722219656</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2029.37222200378</v>
+        <v>2029.3722219656</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0573727895357632</v>
+        <v>0.0573727895175425</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.194572987608239</v>
+        <v>0.194572987594834</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.05905053977451</v>
+        <v>0.0590505397552135</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00397642913613</v>
+        <v>1.00397642915044</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.990990541810808</v>
+        <v>0.990996454106767</v>
       </c>
     </row>
     <row r="53">
@@ -4660,46 +4660,46 @@
         <v>2354.10436983294</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.10270873090534</v>
+        <v>1.10270873085725</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2166.5878408308</v>
+        <v>2166.58784092126</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2131.12559168089</v>
+        <v>2131.11288463544</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2166.01029439176</v>
+        <v>2166.01025569274</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2134.8378804439</v>
+        <v>2134.837880537</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2134.8378804439</v>
+        <v>2134.837880537</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2155.07297264865</v>
+        <v>2155.07297286883</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2155.07297264865</v>
+        <v>2155.07297286883</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.060098090018804</v>
+        <v>0.0600980901397866</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.218221643025046</v>
+        <v>0.218221643150569</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0619407072206548</v>
+        <v>0.0619407073491312</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0.994685252097724</v>
+        <v>0.99468525215782</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>1.01123696372529</v>
+        <v>1.01124299346418</v>
       </c>
     </row>
     <row r="54">
@@ -4719,46 +4719,46 @@
         <v>2600.12971883191</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.06458670795858</v>
+        <v>1.06458670798936</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.0387981799010197</v>
+        <v>0.0387981839892411</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2304.12803045451</v>
+        <v>2304.12803076142</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2214.41280141746</v>
+        <v>2214.39983712701</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2260.00242128978</v>
+        <v>2260.00238718167</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2442.38416598103</v>
+        <v>2442.38416591042</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2309.49211687309</v>
+        <v>2309.49211773057</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2284.91025398779</v>
+        <v>2284.9102544896</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2284.91025398779</v>
+        <v>2284.9102544896</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0585021624203597</v>
+        <v>0.0585021625378117</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.247358193357784</v>
+        <v>0.247358193614909</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0602472783924195</v>
+        <v>0.0602472785169477</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>0.991659414662418</v>
+        <v>0.991659414748118</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>1.0318357320393</v>
+        <v>1.03184177318856</v>
       </c>
     </row>
     <row r="55">
@@ -4778,46 +4778,46 @@
         <v>2154.1851770688</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.902912276987453</v>
+        <v>0.902912276912069</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2401.05607408335</v>
+        <v>2401.05607428306</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2297.07233894525</v>
+        <v>2297.0594153455</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2350.59959160727</v>
+        <v>2350.59956710554</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2385.81890176108</v>
+        <v>2385.81890196027</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2385.81890176108</v>
+        <v>2385.81890196027</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2394.29726845533</v>
+        <v>2394.29726874957</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2394.29726845533</v>
+        <v>2394.29726874957</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0467630242934475</v>
+        <v>0.0467630241967157</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.24949074745615</v>
+        <v>0.24949074761044</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0478736590536244</v>
+        <v>0.0478736589522617</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.997185069644573</v>
+        <v>0.997185069684175</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.04232558455461</v>
+        <v>1.0423314489623</v>
       </c>
     </row>
     <row r="56">
@@ -4837,46 +4837,46 @@
         <v>2321.41186175029</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.930030788158179</v>
+        <v>0.930030788187588</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2511.24095778869</v>
+        <v>2511.24095780106</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2378.55234998304</v>
+        <v>2378.53983861563</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2436.46145889083</v>
+        <v>2436.46145049281</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2496.05915342608</v>
+        <v>2496.05915334715</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2496.05915342608</v>
+        <v>2496.05915334715</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2517.01602331903</v>
+        <v>2517.01602329004</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2517.01602331903</v>
+        <v>2517.01602329004</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.04998431045732</v>
+        <v>0.049984310322911</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.240292931985517</v>
+        <v>0.240292931994563</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0512546025426799</v>
+        <v>0.0512546024013818</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00229968594309</v>
+        <v>1.00229968592661</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05821342268837</v>
+        <v>1.05821898898906</v>
       </c>
     </row>
     <row r="57">
@@ -4896,46 +4896,46 @@
         <v>2970.00973852471</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.1040407630798</v>
+        <v>1.10404076314436</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>2671.11549504705</v>
+        <v>2671.11549446224</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2458.35644685139</v>
+        <v>2458.34480094128</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2516.42377323783</v>
+        <v>2516.42378904624</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>2690.12688466289</v>
+        <v>2690.12688450559</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2690.12688466289</v>
+        <v>2690.12688450559</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>2664.04752424559</v>
+        <v>2664.04752390576</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>2664.04752424559</v>
+        <v>2664.04752390576</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0567725097790841</v>
+        <v>0.0567725096630412</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.236175089222803</v>
+        <v>0.236175088938815</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0584150039429143</v>
+        <v>0.0584150038200928</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>0.99735392542383</v>
+        <v>0.997353925514965</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.08367016006066</v>
+        <v>1.08367529359011</v>
       </c>
     </row>
     <row r="58">
@@ -4955,46 +4955,46 @@
         <v>2943.99757674031</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.0590387244556</v>
+        <v>1.05903872482353</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>2773.86897753295</v>
+        <v>2773.86897748768</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2536.061683623</v>
+        <v>2536.05144589803</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2589.62027321829</v>
+        <v>2589.62032298285</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>2779.8771742305</v>
+        <v>2779.87717326472</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>2779.8771742305</v>
+        <v>2779.87717326472</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>2771.49083862357</v>
+        <v>2771.49083869832</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>2771.49083862357</v>
+        <v>2771.49083869832</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0395387923556132</v>
+        <v>0.0395387925101468</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.212953915273724</v>
+        <v>0.212953915040048</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0403308549866808</v>
+        <v>0.0403308551474468</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.999142663576166</v>
+        <v>0.999142663619421</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.09283258231489</v>
+        <v>1.09283699397388</v>
       </c>
     </row>
     <row r="59">
@@ -5014,46 +5014,46 @@
         <v>2579.42813442157</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.909504035509104</v>
+        <v>0.909504034743336</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>2887.05645864333</v>
+        <v>2887.05646058068</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2611.38997089422</v>
+        <v>2611.38178086369</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>2656.0532129594</v>
+        <v>2656.05330799696</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>2836.08212137037</v>
+        <v>2836.08212375825</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2836.08212137037</v>
+        <v>2836.08212375825</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>2863.46680740126</v>
+        <v>2863.46680902009</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>2863.46680740126</v>
+        <v>2863.46680902009</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0326476768602206</v>
+        <v>0.0326476773985867</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.195952919099564</v>
+        <v>0.19595291962871</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0331864596108047</v>
+        <v>0.0331864601670373</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.991829168712152</v>
+        <v>0.991829168607307</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.0965297559218</v>
+        <v>1.0965331955686</v>
       </c>
     </row>
     <row r="60">
@@ -5073,46 +5073,46 @@
         <v>2838.16101860859</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.926665452527764</v>
+        <v>0.926665452286034</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.531286391690894</v>
+        <v>0.531286403882316</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>2932.74824382131</v>
+        <v>2932.74824522033</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2684.21560394301</v>
+        <v>2684.21020429567</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>2716.67613109337</v>
+        <v>2716.67628403429</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3062.76770205108</v>
+        <v>3062.76770285004</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3001.82581263381</v>
+        <v>3001.82581529915</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>2900.93996825396</v>
+        <v>2900.93996946839</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>2900.93996825396</v>
+        <v>2900.93996946839</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0130017502923655</v>
+        <v>0.0130017501456592</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.15253138691929</v>
+        <v>0.152531387415052</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0130866405560699</v>
+        <v>0.0130866404074437</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989154106345691</v>
+        <v>0.989154106287921</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.08074029671558</v>
+        <v>1.08074247122147</v>
       </c>
     </row>
     <row r="61">
@@ -5132,46 +5132,46 @@
         <v>3062.56234200586</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.10800774015086</v>
+        <v>1.10800774129768</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2804.85507001401</v>
+        <v>2804.85506752173</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2754.55331064139</v>
+        <v>2754.5515523657</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>2773.34271079448</v>
+        <v>2773.34293511939</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>2764.02612637785</v>
+        <v>2764.026123517</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>2764.02612637785</v>
+        <v>2764.026123517</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>2788.18419705627</v>
+        <v>2788.18419560044</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>2788.18419705627</v>
+        <v>2788.18419560044</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0396442529321402</v>
+        <v>-0.0396442538729144</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0465970188898306</v>
+        <v>0.0465970184768634</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0388687020178349</v>
+        <v>-0.0388687029220424</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994056422687945</v>
+        <v>0.994056423052183</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.01220919787065</v>
+        <v>1.01220984345196</v>
       </c>
     </row>
     <row r="62">
@@ -5191,46 +5191,46 @@
         <v>2755.1961460775</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.0504554141974</v>
+        <v>1.05045541530557</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>2624.79759932966</v>
+        <v>2624.79759858391</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>2822.6163252418</v>
+        <v>2822.61917100237</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>2829.33238364472</v>
+        <v>2829.33269293312</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>2622.85872283557</v>
+        <v>2622.8587200686</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>2622.85872283557</v>
+        <v>2622.8587200686</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>2642.56180628708</v>
+        <v>2642.56180611997</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>2642.56180628708</v>
+        <v>2642.56180611997</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.053641730714481</v>
+        <v>-0.0536417302555784</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0465197396793551</v>
+        <v>-0.0465197397653702</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0522283968623504</v>
+        <v>-0.0522283964274155</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.00676783877049</v>
+        <v>1.00676783899286</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.93621006250671</v>
+        <v>0.936209118561872</v>
       </c>
     </row>
     <row r="63">
@@ -5250,46 +5250,46 @@
         <v>2346.01620451565</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.916232320807643</v>
+        <v>0.916232318042915</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>2533.47959554577</v>
+        <v>2533.47960195801</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2888.62380250652</v>
+        <v>2888.63232774124</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>2887.87799830399</v>
+        <v>2887.87840509831</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2560.50365309934</v>
+        <v>2560.50366082565</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>2560.50365309934</v>
+        <v>2560.50366082565</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>2566.55789435482</v>
+        <v>2566.55789890555</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>2566.55789435482</v>
+        <v>2566.55789890555</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.029183167341406</v>
+        <v>-0.0291831655050769</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.103688616986591</v>
+        <v>-0.10368861590407</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0287614510099397</v>
+        <v>-0.0287614492264261</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.01305646939774</v>
+        <v>1.01305646862993</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.888505416360469</v>
+        <v>0.888502795685481</v>
       </c>
     </row>
     <row r="64">
@@ -5309,46 +5309,46 @@
         <v>2313.68685692728</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.927837099084918</v>
+        <v>0.927837097598438</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0.658291170729635</v>
+        <v>0.658291149341802</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>2577.7144654663</v>
+        <v>2577.71446865353</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2952.67004869635</v>
+        <v>2952.68543983607</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2951.18003512815</v>
+        <v>2951.1805493735</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>2493.63477620065</v>
+        <v>2493.63478019568</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>2522.36554838503</v>
+        <v>2522.36555390231</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>2607.63726807194</v>
+        <v>2607.63726987264</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>2607.63726807194</v>
+        <v>2607.63726987264</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0158788895923189</v>
+        <v>0.0158788885097794</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.101106090919404</v>
+        <v>-0.101106090674979</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.016005629098599</v>
+        <v>0.0160056279987328</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01160826887792</v>
+        <v>1.01160826832568</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.883145500535442</v>
+        <v>0.883140897669554</v>
       </c>
     </row>
     <row r="65">
@@ -5368,46 +5368,46 @@
         <v>3129.72211611434</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.1077429832428</v>
+        <v>1.10774298777446</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>2789.05113281841</v>
+        <v>2789.05112368239</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3014.64429497867</v>
+        <v>3014.66784412375</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3019.80210274702</v>
+        <v>3019.80272979584</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>2825.31432241837</v>
+        <v>2825.31431086031</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2825.31432241837</v>
+        <v>2825.31431086031</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>2802.98380563048</v>
+        <v>2802.98379919635</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>2802.98380563048</v>
+        <v>2802.98379919635</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0722399445897131</v>
+        <v>0.072239941603705</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.00530797376652381</v>
+        <v>0.00530797198379518</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0749132327376867</v>
+        <v>0.0749132295279871</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.00499548848285</v>
+        <v>1.00499548946796</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.929789232613367</v>
+        <v>0.92978196740977</v>
       </c>
     </row>
     <row r="66">
@@ -5427,46 +5427,46 @@
         <v>3164.98577161261</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.04147653445631</v>
+        <v>1.04147653724518</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3058.61978728294</v>
+        <v>3058.61978227095</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3074.1668322082</v>
+        <v>3074.19992751249</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3092.16373735672</v>
+        <v>3092.16447542514</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3038.94102930015</v>
+        <v>3038.94102116246</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3038.94102930015</v>
+        <v>3038.94102116246</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3033.33164148955</v>
+        <v>3033.33163983018</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3033.33164148955</v>
+        <v>3033.33163983018</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0789770724510876</v>
+        <v>0.0789770741994995</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.147875381485029</v>
+        <v>0.14787538092968</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0821795100622276</v>
+        <v>0.0821795119543232</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.991732170863953</v>
+        <v>0.991732171946526</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.986716664075999</v>
+        <v>0.986706041036381</v>
       </c>
     </row>
     <row r="67">
@@ -5486,46 +5486,46 @@
         <v>2987.75245463425</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.924963479355918</v>
+        <v>0.924963473286357</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3186.01395678804</v>
+        <v>3186.01398381078</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3130.73962000678</v>
+        <v>3130.78373095221</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3165.71203625171</v>
+        <v>3165.71287322654</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3230.13018493954</v>
+        <v>3230.13020613548</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3230.13018493954</v>
+        <v>3230.13020613548</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3174.02648085416</v>
+        <v>3174.02649905049</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3174.02648085416</v>
+        <v>3174.02649905049</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0453393980198141</v>
+        <v>0.0453394042997462</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.236686103140507</v>
+        <v>0.236686108037532</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0463829399463627</v>
+        <v>0.0463829465175765</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.996237469108277</v>
+        <v>0.996237466369828</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.0138264008194</v>
+        <v>1.0138121223995</v>
       </c>
     </row>
     <row r="68">
@@ -5545,46 +5545,46 @@
         <v>2968.07680589468</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.928422098124019</v>
+        <v>0.928422086934087</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3244.08377128764</v>
+        <v>3244.08377690525</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3183.84260186946</v>
+        <v>3183.89925857635</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3237.62798318621</v>
+        <v>3237.62889289383</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3196.90452423743</v>
+        <v>3196.90456276855</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3196.90452423743</v>
+        <v>3196.90456276855</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3240.51175686929</v>
+        <v>3240.511763084</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3240.51175686929</v>
+        <v>3240.511763084</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0207303018588646</v>
+        <v>0.0207302980437967</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.24270035428098</v>
+        <v>0.242700355806107</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0209466670855356</v>
+        <v>0.0209466631905548</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>0.998898914248157</v>
+        <v>0.998898914434122</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.01779898132105</v>
+        <v>1.01778087178957</v>
       </c>
     </row>
     <row r="69">
@@ -5604,46 +5604,46 @@
         <v>3696.32832846722</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.10731245259413</v>
+        <v>1.10731247694206</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3306.91303370372</v>
+        <v>3306.9130044322</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3233.01784039435</v>
+        <v>3233.08860606535</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3305.41465265782</v>
+        <v>3305.41559078539</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3338.10779406277</v>
+        <v>3338.10772066342</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3338.10779406277</v>
+        <v>3338.10772066342</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3320.79186035994</v>
+        <v>3320.79183739007</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3320.79186035994</v>
+        <v>3320.79183739007</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0244719996629828</v>
+        <v>0.0244719908281794</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.18473458665345</v>
+        <v>0.184734581178167</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0247738966910001</v>
+        <v>0.0247738876373242</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00419691310741</v>
+        <v>1.00419691505016</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.02714925320514</v>
+        <v>1.02712676391244</v>
       </c>
     </row>
     <row r="70">
@@ -5663,46 +5663,46 @@
         <v>3523.50222767909</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.0332707694802</v>
+        <v>1.03327076451448</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>3437.22800102012</v>
+        <v>3437.22799115428</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>3277.81556188106</v>
+        <v>3277.90199741475</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>3366.37150186943</v>
+        <v>3366.37240160894</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>3410.0473290768</v>
+        <v>3410.0473454649</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>3410.0473290768</v>
+        <v>3410.0473454649</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>3438.01896073795</v>
+        <v>3438.01896005669</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>3438.01896073795</v>
+        <v>3438.01896005669</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0346921553487963</v>
+        <v>0.0346921620676269</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.13341347636148</v>
+        <v>0.133413476756918</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0353009478785278</v>
+        <v>0.0353009548345395</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00023011558081</v>
+        <v>1.00023011825356</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.0488750498106</v>
+        <v>1.04884739164509</v>
       </c>
     </row>
     <row r="71">
@@ -5722,46 +5722,46 @@
         <v>3347.59534135146</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.931472808691917</v>
+        <v>0.93147279886935</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>3575.99136282767</v>
+        <v>3575.99142868862</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3317.85167385023</v>
+        <v>3317.95529356676</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>3417.96145373096</v>
+        <v>3417.96222072161</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>3593.87339073541</v>
+        <v>3593.87342863353</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3593.87339073541</v>
+        <v>3593.87342863353</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>3574.58887138213</v>
+        <v>3574.58891410043</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>3574.58887138213</v>
+        <v>3574.58891410043</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0389547465265571</v>
+        <v>0.0389547586752615</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.126200078337145</v>
+        <v>0.126200085339479</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0397234314888342</v>
+        <v>0.0397234441201268</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999607803458332</v>
+        <v>0.999607796993881</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.07738055307155</v>
+        <v>1.07734691936063</v>
       </c>
     </row>
     <row r="72">
@@ -5781,46 +5781,46 @@
         <v>3450.41139520334</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.932402153503304</v>
+        <v>0.93240213367667</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>3712.7104372995</v>
+        <v>3712.71044236836</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>3352.82472867699</v>
+        <v>3352.94694630605</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>3457.86581028836</v>
+        <v>3457.8663181998</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>3700.5613749809</v>
+        <v>3700.56145366978</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>3700.5613749809</v>
+        <v>3700.56145366978</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>3694.90475201341</v>
+        <v>3694.9047622052</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>3694.90475201341</v>
+        <v>3694.9047622052</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0331046080134791</v>
+        <v>0.0331045988212647</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.140222603476408</v>
+        <v>0.140222604434785</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0336586625652302</v>
+        <v>0.0336586530636183</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.995204127661774</v>
+        <v>0.995204129048155</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.10202741002552</v>
+        <v>1.10198724327442</v>
       </c>
     </row>
     <row r="73">
@@ -5840,46 +5840,46 @@
         <v>4175.47231114959</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.10327302283257</v>
+        <v>1.10327306787413</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>3773.83928862889</v>
+        <v>3773.83923255207</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3382.60579230954</v>
+        <v>3382.74785625178</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>3484.64543327257</v>
+        <v>3484.64552015948</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>3784.62286735642</v>
+        <v>3784.6227128477</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>3784.62286735642</v>
+        <v>3784.6227128477</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>3751.22947621377</v>
+        <v>3751.22943054932</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>3751.22947621377</v>
+        <v>3751.22943054932</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0151288700372043</v>
+        <v>0.0151288551056733</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.129618968593585</v>
+        <v>0.12961896265607</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0152438907037229</v>
+        <v>0.0152438755445774</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.994008803585451</v>
+        <v>0.994008806255517</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.10897624687521</v>
+        <v>1.10892966013312</v>
       </c>
     </row>
     <row r="74">
@@ -5899,46 +5899,46 @@
         <v>3842.8691195722</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.02885010119391</v>
+        <v>1.02885008806282</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>3722.99356096208</v>
+        <v>3722.99355105471</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>3407.28326610002</v>
+        <v>3407.44618309015</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>3498.07466223805</v>
+        <v>3498.07412839394</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>3735.11079516133</v>
+        <v>3735.1108428321</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3735.11079516133</v>
+        <v>3735.1108428321</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>3710.69615389197</v>
+        <v>3710.69615261125</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>3710.69615389197</v>
+        <v>3710.69615261125</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.0108641449963765</v>
+        <v>-0.0108641331683229</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0793123005626171</v>
+        <v>0.0793123004039717</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.010805343309125</v>
+        <v>-0.0108053316088775</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996696903481367</v>
+        <v>0.996696905789704</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.0890483309124</v>
+        <v>1.08899626090238</v>
       </c>
     </row>
     <row r="75">
@@ -5958,46 +5958,46 @@
         <v>3354.26213069839</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.934871258463822</v>
+        <v>0.934871244382074</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>3623.64166111755</v>
+        <v>3623.64173615547</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>3427.19681207245</v>
+        <v>3427.38125829279</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>3499.42772390964</v>
+        <v>3499.42633065995</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>3587.9401578888</v>
+        <v>3587.94021193311</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3587.9401578888</v>
+        <v>3587.94021193311</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>3612.69062482673</v>
+        <v>3612.69064332055</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>3612.69062482673</v>
+        <v>3612.69064332055</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0267666814106744</v>
+        <v>-0.0267666759464055</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0106590589339208</v>
+        <v>0.0106590520296816</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0264116287081184</v>
+        <v>-0.0264116233881697</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.996977892044811</v>
+        <v>0.996977876503173</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.05412406200335</v>
+        <v>1.05406733919064</v>
       </c>
     </row>
     <row r="76">
@@ -6017,46 +6017,46 @@
         <v>3413.57383659744</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.937755960856985</v>
+        <v>0.937755933724336</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>0.309540310776156</v>
+        <v>0.30953971517834</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>3494.76989989924</v>
+        <v>3494.7698596411</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>3442.89098445655</v>
+        <v>3443.09720374362</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3491.16402567681</v>
+        <v>3491.16149828646</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>3640.15157363317</v>
+        <v>3640.15167895584</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>3539.771388368</v>
+        <v>3539.77130658389</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>3496.41160161194</v>
+        <v>3496.41152557272</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>3496.41160161194</v>
+        <v>3496.41152557272</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.0327156342865674</v>
+        <v>-0.0327156611534824</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>-0.0537207759667725</v>
+        <v>-0.0537207991564077</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0321862664950378</v>
+        <v>-0.0321862924972067</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00046975960069</v>
+        <v>1.00046974936764</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01554525467028</v>
+        <v>1.01548440798335</v>
       </c>
     </row>
     <row r="77">
@@ -6076,46 +6076,46 @@
         <v>3636.39564268968</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1.09590611600938</v>
+        <v>1.09590618029177</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>3347.91171679836</v>
+        <v>3347.91162574085</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>3455.01080207315</v>
+        <v>3455.23849067262</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>3476.18553709892</v>
+        <v>3476.18157200876</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>3318.16347182294</v>
+        <v>3318.16327718997</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>3318.16347182294</v>
+        <v>3318.16327718997</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>3368.06470160639</v>
+        <v>3368.06460190881</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>3368.06470160639</v>
+        <v>3368.06460190881</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.0373988789916308</v>
+        <v>-0.0373988868446928</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.102143784334441</v>
+        <v>-0.102143799981969</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.0367081781636845</v>
+        <v>-0.0367081857284749</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00601956876787</v>
+        <v>1.00601956635086</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.97483478187258</v>
+        <v>0.974770514683969</v>
       </c>
     </row>
     <row r="78">
@@ -6135,46 +6135,46 @@
         <v>3401.60556878379</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.03199027935402</v>
+        <v>1.03199025673032</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>3327.05331145544</v>
+        <v>3327.05330459954</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>3464.26183399554</v>
+        <v>3464.51001162403</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>3457.63726454879</v>
+        <v>3457.63154160367</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>3296.16047441168</v>
+        <v>3296.16054667142</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>3296.16047441168</v>
+        <v>3296.16054667142</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>3342.31678574351</v>
+        <v>3342.31678885195</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>3342.31678574351</v>
+        <v>3342.31678885195</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>-0.00767409193435931</v>
+        <v>-0.00767406140348455</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.0992750020133243</v>
+        <v>-0.0992750008647497</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>-0.00764472126993276</v>
+        <v>-0.00764469097245757</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00458768551604</v>
+        <v>1.00458768852044</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>0.964799124865403</v>
+        <v>0.96473001308638</v>
       </c>
     </row>
     <row r="79">
@@ -6194,46 +6194,46 @@
         <v>3222.50375079941</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.931687246497719</v>
+        <v>0.931687229649461</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>3397.44349390417</v>
+        <v>3397.44350130135</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>3471.26411971558</v>
+        <v>3471.53098713366</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>3437.87410407286</v>
+        <v>3437.86630537387</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>3458.78272232774</v>
+        <v>3458.78278487498</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>3458.78272232774</v>
+        <v>3458.78278487498</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>3394.94142145267</v>
+        <v>3394.94149528866</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>3394.94142145267</v>
+        <v>3394.94149528866</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0156222915513028</v>
+        <v>0.0156223123701046</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>-0.0602734155749943</v>
+        <v>-0.0602733999476232</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0157449574898534</v>
+        <v>0.0157449786364465</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.999263542585478</v>
+        <v>0.999263562142613</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.978012995948816</v>
+        <v>0.977937834307438</v>
       </c>
     </row>
     <row r="80">
@@ -6253,46 +6253,46 @@
         <v>3185.85231014052</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.946469005392261</v>
+        <v>0.946468977839331</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>3418.68887831757</v>
+        <v>3418.6893129114</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>3476.53263537542</v>
+        <v>3476.81541932174</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>3418.44356776688</v>
+        <v>3418.43340664742</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>3366.03976674351</v>
+        <v>3366.03986473325</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>3366.03976674351</v>
+        <v>3366.03986473325</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>3389.41505356302</v>
+        <v>3389.41578161894</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>3389.41505356302</v>
+        <v>3389.41578161894</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00162915057081782</v>
+        <v>-0.00162895751684521</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.0306018170170768</v>
+        <v>-0.03060158770534</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00162782422539653</v>
+        <v>-0.00162763148566325</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.991437119376317</v>
+        <v>0.991437206305381</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.974941244351935</v>
+        <v>0.974862157704119</v>
       </c>
     </row>
     <row r="81">
@@ -6312,46 +6312,46 @@
         <v>3869.93013865163</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1.08365343917505</v>
+        <v>1.08365350072599</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.0220956203995741</v>
+        <v>0.0221049410198844</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>3362.17979282867</v>
+        <v>3362.18051897485</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>3480.57455624382</v>
+        <v>3480.86934268206</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>3400.99771081788</v>
+        <v>3400.98497114986</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>3571.18798201543</v>
+        <v>3571.18777917386</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>3366.79795843734</v>
+        <v>3366.80061213428</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>3344.65721675468</v>
+        <v>3344.6585709803</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>3344.65721675468</v>
+        <v>3344.6585709803</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0132931439098025</v>
+        <v>-0.0132929538204838</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>-0.00694983229999813</v>
+        <v>-0.00694940082658957</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0132051802747761</v>
+        <v>-0.0132049926956033</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.994788328657688</v>
+        <v>0.99478851659045</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.960949740540593</v>
+        <v>0.960868749070368</v>
       </c>
     </row>
     <row r="82">
@@ -6371,46 +6371,46 @@
         <v>3413.56946580066</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.04104195247535</v>
+        <v>1.04104194881825</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>3322.86122229199</v>
+        <v>3322.86156611449</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3483.82799954664</v>
+        <v>3484.12955698681</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>3386.92656940777</v>
+        <v>3386.91115689717</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>3278.99318340054</v>
+        <v>3278.99319491939</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>3278.99318340054</v>
+        <v>3278.99319491939</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>3315.67935461701</v>
+        <v>3315.68002901054</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>3315.67935461701</v>
+        <v>3315.68002901054</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.00870167586133361</v>
+        <v>-0.00870187735819057</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.00796975057544558</v>
+        <v>-0.0079695497237865</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.00866392585539477</v>
+        <v>-0.00866412560647778</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.99783864952686</v>
+        <v>0.99783874923434</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.951734515897021</v>
+        <v>0.95165233518987</v>
       </c>
     </row>
     <row r="83">
@@ -6430,46 +6430,46 @@
         <v>3098.85650879477</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.928375860822446</v>
+        <v>0.928375855026377</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>3316.3782545089</v>
+        <v>3316.37831348504</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3486.65997213614</v>
+        <v>3486.96156905159</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>3377.44918095655</v>
+        <v>3377.43120011024</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>3337.93309322961</v>
+        <v>3337.93311406912</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>3337.93309322961</v>
+        <v>3337.93311406912</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>3330.61102290117</v>
+        <v>3330.61113528841</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>3330.61102290117</v>
+        <v>3330.61113528841</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.00449324135948639</v>
+        <v>0.00449307170795664</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.018948897952993</v>
+        <v>-0.0189488861853786</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.00450335110461397</v>
+        <v>0.00450318068909827</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00429166014851</v>
+        <v>1.00429167617744</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.95524400128431</v>
+        <v>0.955161411828893</v>
       </c>
     </row>
     <row r="84">
@@ -6489,46 +6489,46 @@
         <v>3199.75362495821</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.950162769268136</v>
+        <v>0.950162657437829</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>3392.20046476105</v>
+        <v>3392.20064742768</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>3489.30945910447</v>
+        <v>3489.60267546572</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>3373.24491595421</v>
+        <v>3373.22474720009</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>3367.58472174491</v>
+        <v>3367.58511809603</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>3367.58472174491</v>
+        <v>3367.58511809603</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>3378.01223530857</v>
+        <v>3378.01237259886</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>3378.01223530857</v>
+        <v>3378.01237259886</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.0141316629152885</v>
+        <v>0.0141316698138886</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.00336424370407729</v>
+        <v>-0.0033644172786117</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.0142319868881324</v>
+        <v>0.0142319938849134</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.995817396524801</v>
+        <v>0.995817383373364</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.968103366840824</v>
+        <v>0.968022060605521</v>
       </c>
     </row>
     <row r="85">
@@ -6548,46 +6548,46 @@
         <v>3684.19222817274</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1.07131423256144</v>
+        <v>1.07131431492233</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>3391.14493291041</v>
+        <v>3391.14476359253</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>3491.92249124446</v>
+        <v>3492.19703003412</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>3374.79556445208</v>
+        <v>3374.77395414752</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>3438.94640451484</v>
+        <v>3438.94614013427</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>3438.94640451484</v>
+        <v>3438.94614013427</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>3383.31275789184</v>
+        <v>3383.31261138669</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>3383.31275789184</v>
+        <v>3383.31261138669</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>0.00156789495386156</v>
+        <v>0.00156781100925191</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0115573999462544</v>
+        <v>0.011556946571998</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>0.00156912474379789</v>
+        <v>0.00156904066747221</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>0.99769040392743</v>
+        <v>0.99769041053926</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.968896865945639</v>
+        <v>0.968820654244025</v>
       </c>
     </row>
     <row r="86">
@@ -6607,46 +6607,46 @@
         <v>3473.96328435329</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.0566309642424</v>
+        <v>1.05663111002466</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>3321.51341393432</v>
+        <v>3321.51294092053</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3494.5690213881</v>
+        <v>3494.81252558838</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>3382.55461553044</v>
+        <v>3382.53277878781</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>3287.77350079278</v>
+        <v>3287.7730471822</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>3287.77350079278</v>
+        <v>3287.7730471822</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>3328.83132349347</v>
+        <v>3328.83104102872</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>3328.83132349347</v>
+        <v>3328.83104102872</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>-0.0162340469021641</v>
+        <v>-0.0162340884539174</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.00396659853678138</v>
+        <v>0.00396630914416152</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>-0.0161029849431719</v>
+        <v>-0.016103025825817</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00220318530958</v>
+        <v>1.00220324299148</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.952572778823297</v>
+        <v>0.952506326635729</v>
       </c>
     </row>
     <row r="87">
@@ -6666,46 +6666,46 @@
         <v>3047.37400305265</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.923213937143551</v>
+        <v>0.923213925468472</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>3320.9573753931</v>
+        <v>3320.95783385677</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>3497.28589231317</v>
+        <v>3497.4837731539</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>3397.29631246991</v>
+        <v>3397.27603988618</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>3300.83188787347</v>
+        <v>3300.83192961621</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>3300.83188787347</v>
+        <v>3300.83192961621</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>3323.70480896358</v>
+        <v>3323.70514118585</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>3323.70480896358</v>
+        <v>3323.70514118585</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>-0.00154122140567001</v>
+        <v>-0.00154103659623378</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>-0.00207355764155681</v>
+        <v>-0.00207349156717496</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>-0.0015400343338845</v>
+        <v>-0.00153984980904409</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00082730166633</v>
+        <v>1.00082726353857</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.950366916318993</v>
+        <v>0.950313241393157</v>
       </c>
     </row>
     <row r="88">
@@ -6725,46 +6725,46 @@
         <v>3228.33181776595</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.948008727460259</v>
+        <v>0.948008254479691</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>3341.64430628085</v>
+        <v>3341.64523598115</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3499.98069959707</v>
+        <v>3500.11598408208</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>3419.32099297739</v>
+        <v>3419.30475754982</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>3405.38195931459</v>
+        <v>3405.3836583288</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>3405.38195931459</v>
+        <v>3405.3836583288</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>3341.54748557253</v>
+        <v>3341.54817556441</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>3341.54748557253</v>
+        <v>3341.54817556441</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.00535395164109569</v>
+        <v>0.00535405817439583</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>-0.0107947358375117</v>
+        <v>-0.0107945717813923</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.00536830965278012</v>
+        <v>0.00536841675798971</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999971026028073</v>
+        <v>0.999970954302482</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.954733117801828</v>
+        <v>0.954696413136363</v>
       </c>
     </row>
     <row r="89">
@@ -6784,46 +6784,46 @@
         <v>3463.84324480454</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>1.06429345727511</v>
+        <v>1.06429367957954</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>3332.12799874782</v>
+        <v>3332.12757813304</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3502.43825506444</v>
+        <v>3502.49146232209</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>3448.44667263683</v>
+        <v>3448.43773133457</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>3254.59413578747</v>
+        <v>3254.59345598385</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>3254.59413578747</v>
+        <v>3254.59345598385</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>3321.06380016145</v>
+        <v>3321.06343116432</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>3321.06380016145</v>
+        <v>3321.06343116432</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>-0.00614886538348732</v>
+        <v>-0.00614918298030789</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>-0.0183988186091274</v>
+        <v>-0.0183988851674152</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>-0.00612999979785589</v>
+        <v>-0.00613031544775788</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.996679539744412</v>
+        <v>0.996679554816171</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.948214803033079</v>
+        <v>0.948200293102931</v>
       </c>
     </row>
     <row r="90">
@@ -6843,46 +6843,46 @@
         <v>3610.11150456841</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.07134985524464</v>
+        <v>1.07135043242759</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>3284.25452394873</v>
+        <v>3284.25287975558</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>3504.38424632723</v>
+        <v>3504.33330411953</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>3484.42167186385</v>
+        <v>3484.42415530016</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>3369.68496975626</v>
+        <v>3369.6831543608</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>3369.68496975626</v>
+        <v>3369.6831543608</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>3302.47442930985</v>
+        <v>3302.47336207343</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>3302.47442930985</v>
+        <v>3302.47336207343</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>-0.00561313878353098</v>
+        <v>-0.00561335083812573</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>-0.00791776200782812</v>
+        <v>-0.00791799842960716</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>-0.00559741455454599</v>
+        <v>-0.00559762542216091</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.0055476532736</v>
+        <v>1.00554783172458</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.942383653496617</v>
+        <v>0.942397048303366</v>
       </c>
     </row>
     <row r="91">
@@ -6902,46 +6902,46 @@
         <v>2954.63346329572</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.918748267925671</v>
+        <v>0.918748256027158</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>3303.67326533652</v>
+        <v>3303.67393148796</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3505.38945842286</v>
+        <v>3505.20966946602</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>3526.02504838981</v>
+        <v>3526.04400212958</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>3215.9336419394</v>
+        <v>3215.93368358827</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>3215.9336419394</v>
+        <v>3215.93368358827</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>3305.91322406491</v>
+        <v>3305.91386832228</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>3305.91322406491</v>
+        <v>3305.91386832228</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.00104073648394179</v>
+        <v>0.00104125452693702</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>-0.00535293773703771</v>
+        <v>-0.00535284332027985</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.00104127823808109</v>
+        <v>0.00104179682063754</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.00067802066018</v>
+        <v>1.00067801389628</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>0.943094415977476</v>
+        <v>0.943142972906924</v>
       </c>
     </row>
     <row r="92">
@@ -6961,46 +6961,46 @@
         <v>3221.79961592558</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.941468399788101</v>
+        <v>0.941467214287612</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>3343.09834238811</v>
+        <v>3343.10238356452</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3504.94048934087</v>
+        <v>3504.60456200958</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>3571.46217643555</v>
+        <v>3571.50353950111</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>3422.10064262456</v>
+        <v>3422.10495175177</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>3422.10064262456</v>
+        <v>3422.10495175177</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>3370.53782004135</v>
+        <v>3370.54045994396</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>3370.53782004135</v>
+        <v>3370.54045994396</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0193595711076762</v>
+        <v>0.0193601594559817</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.00867572123214866</v>
+        <v>0.00867630297583633</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0195481827853239</v>
+        <v>0.0195487826349461</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.00820779852789</v>
+        <v>1.0082073694525</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>0.96165336623881</v>
+        <v>0.961746296994849</v>
       </c>
     </row>
     <row r="93">
@@ -7020,46 +7020,46 @@
         <v>3638.1623004355</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1.06316332979257</v>
+        <v>1.0631627395856</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>3486.19604906964</v>
+        <v>3486.1939794849</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>3502.34302718551</v>
+        <v>3501.82118790707</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>3617.38797318966</v>
+        <v>3617.45848350033</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>3422.01635297686</v>
+        <v>3422.01825268405</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3422.01635297686</v>
+        <v>3422.01825268405</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>3497.89514791856</v>
+        <v>3497.89401887673</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>3497.89514791856</v>
+        <v>3497.89401887673</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.0370890791333275</v>
+        <v>0.0370879731271908</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.0532453931624313</v>
+        <v>0.0532451702226022</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.0377854617503304</v>
+        <v>0.0377843139538758</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>1.00335583503746</v>
+        <v>1.00335610682041</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>0.998730027518028</v>
+        <v>0.998878535247916</v>
       </c>
     </row>
     <row r="94">
@@ -7079,46 +7079,46 @@
         <v>4037.4781476365</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.08375662952114</v>
+        <v>1.08376030214283</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>3715.4243105474</v>
+        <v>3715.41983903915</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>3496.85098515684</v>
+        <v>3496.11119105892</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>3659.71054817166</v>
+        <v>3659.81755727407</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>3725.44724309596</v>
+        <v>3725.43461838705</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>3725.44724309596</v>
+        <v>3725.43461838705</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>3710.2510712467</v>
+        <v>3710.24757275826</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>3710.2510712467</v>
+        <v>3710.24757275826</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.0589381472389278</v>
+        <v>0.0589375270910436</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.123476093658072</v>
+        <v>0.123475397369689</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0607096308917383</v>
+        <v>0.0607089730951089</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>0.998607631627425</v>
+        <v>0.998607891838617</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.06102635971498</v>
+        <v>1.06124987736288</v>
       </c>
     </row>
     <row r="95">
@@ -7138,46 +7138,46 @@
         <v>3625.34060687029</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.913622790484195</v>
+        <v>0.913620636398695</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>3928.008760828</v>
+        <v>3928.0111548335</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>3487.66807228352</v>
+        <v>3486.67633853107</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>3693.36115280002</v>
+        <v>3693.51228281507</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>3968.09344581801</v>
+        <v>3968.10280157489</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>3968.09344581801</v>
+        <v>3968.10280157489</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>3895.94800609311</v>
+        <v>3895.95088333291</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>3895.94800609311</v>
+        <v>3895.95088333291</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0488374917125554</v>
+        <v>0.0488391731588138</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.17847860546766</v>
+        <v>0.178479246136584</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0500496950962437</v>
+        <v>0.050051460699859</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.991837911601771</v>
+        <v>0.991838039598962</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.11706387343858</v>
+        <v>1.11738243102148</v>
       </c>
     </row>
     <row r="96">
@@ -7197,46 +7197,46 @@
         <v>3659.99110295258</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.933157513270865</v>
+        <v>0.933156223236844</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>3929.74218136607</v>
+        <v>3929.75369453499</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3474.14087025543</v>
+        <v>3472.86172453152</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>3713.59972196782</v>
+        <v>3713.80226742166</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>3922.15788964045</v>
+        <v>3922.16331179484</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>3922.15788964045</v>
+        <v>3922.16331179484</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>3929.54199045825</v>
+        <v>3929.54903246392</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>3929.54199045825</v>
+        <v>3929.54903246392</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.00858583698892108</v>
+        <v>0.00858689053428604</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.165850140322725</v>
+        <v>0.165851316476779</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.00862280100058022</v>
+        <v>0.00862386363101697</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>0.99994905749574</v>
+        <v>0.999947919873106</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.13108308995235</v>
+        <v>1.13150172513534</v>
       </c>
     </row>
     <row r="97">
@@ -7256,46 +7256,46 @@
         <v>4183.39210452291</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>1.0710830818037</v>
+        <v>1.07108089674131</v>
       </c>
       <c r="G97" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>3977.79064053321</v>
+        <v>3977.78491263007</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3455.91622662093</v>
+        <v>3454.31333480768</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>3717.05985203325</v>
+        <v>3717.32007098594</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>3905.75873673412</v>
+        <v>3905.76670469111</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>3905.75873673412</v>
+        <v>3905.76670469111</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>3966.84967055264</v>
+        <v>3966.84661827499</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>3966.84967055264</v>
+        <v>3966.84661827499</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.00944936859709715</v>
+        <v>0.00944680708434474</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.134067632905788</v>
+        <v>0.134067126353031</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.00949415483661453</v>
+        <v>0.00949156900777526</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.997249485714738</v>
+        <v>0.997250154396143</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.14784312188935</v>
+        <v>1.14837486753235</v>
       </c>
     </row>
     <row r="98">
@@ -7315,46 +7315,46 @@
         <v>4473.66539441506</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.08223629137013</v>
+        <v>1.08224507955248</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>4033.26368927765</v>
+        <v>4033.24995184982</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>3432.92099956547</v>
+        <v>3430.957968599</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>3701.41793019284</v>
+        <v>3701.74005862189</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>4133.72331910189</v>
+        <v>4133.68975192289</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>4133.72331910189</v>
+        <v>4133.68975192289</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>4003.2696039385</v>
+        <v>4003.25900758175</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>4003.2696039385</v>
+        <v>4003.25900758175</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.00913918239565979</v>
+        <v>0.0091373049131292</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.0789753919788898</v>
+        <v>0.0789735534024401</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.0091810722388137</v>
+        <v>0.00917917752075903</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.992563321505884</v>
+        <v>0.992564074970283</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.16614090578992</v>
+        <v>1.16680502769798</v>
       </c>
     </row>
     <row r="99">
@@ -7374,46 +7374,46 @@
         <v>3517.77670169052</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.916117971687646</v>
+        <v>0.916113968095718</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>3869.39006863881</v>
+        <v>3869.39383354281</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>3405.36319884331</v>
+        <v>3403.00458350111</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>3665.29383806663</v>
+        <v>3665.67882861203</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>3839.8730408161</v>
+        <v>3839.88982179014</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>3839.8730408161</v>
+        <v>3839.88982179014</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>3859.91579726282</v>
+        <v>3859.92202453469</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>3859.91579726282</v>
+        <v>3859.92202453469</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.036466059156076</v>
+        <v>-0.0364617989102279</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>-0.00924863698743694</v>
+        <v>-0.00924777028179746</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0358091812089408</v>
+        <v>-0.0358050735102584</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.99755148196281</v>
+        <v>0.997552120715649</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.13348138564894</v>
+        <v>1.13426882915435</v>
       </c>
     </row>
     <row r="100">
@@ -7433,46 +7433,46 @@
         <v>3357.72554729946</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.925964177126254</v>
+        <v>0.925957815191627</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>3667.42615537273</v>
+        <v>3667.46689505616</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>3373.88883565847</v>
+        <v>3371.10134447421</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>3609.46898421921</v>
+        <v>3609.91272770535</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>3626.19378831719</v>
+        <v>3626.21870263559</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>3626.19378831719</v>
+        <v>3626.21870263559</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>3696.23456450144</v>
+        <v>3696.25971721269</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>3696.23456450144</v>
+        <v>3696.25971721269</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.0433307528711487</v>
+        <v>-0.0433255612556913</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.0593726766435712</v>
+        <v>-0.0593679613930035</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.042405389484779</v>
+        <v>-0.0424004180088922</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00785521177748</v>
+        <v>1.00785087445379</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.09554130101624</v>
+        <v>1.09645464182543</v>
       </c>
     </row>
     <row r="101">
@@ -7492,46 +7492,46 @@
         <v>3992.99553442729</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>1.08132794765883</v>
+        <v>1.08131799115848</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>3660.38108587428</v>
+        <v>3660.36660910002</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>3339.41548986616</v>
+        <v>3336.16946975243</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>3535.59767322891</v>
+        <v>3536.08915761677</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>3692.67764055527</v>
+        <v>3692.71164178944</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>3692.67764055527</v>
+        <v>3692.71164178944</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>3672.33004388321</v>
+        <v>3672.32119400521</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>3672.33004388321</v>
+        <v>3672.32119400521</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.00648826623606423</v>
+        <v>-0.0064974810520726</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.0742452200434424</v>
+        <v>-0.0742467386848067</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.00646726288634769</v>
+        <v>-0.00647641806553678</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.00326440272982</v>
+        <v>1.00326595288993</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.09969246265621</v>
+        <v>1.10075978672562</v>
       </c>
     </row>
     <row r="102">
@@ -7551,46 +7551,46 @@
         <v>3941.5912142825</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.07173369428551</v>
+        <v>1.07177108804795</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>3675.09761104776</v>
+        <v>3675.02852164082</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>3303.01843191701</v>
+        <v>3299.28962591876</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>3445.41783369457</v>
+        <v>3445.93704993582</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>3677.77110610508</v>
+        <v>3677.6427898064</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>3677.77110610508</v>
+        <v>3677.6427898064</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>3676.99721560962</v>
+        <v>3676.94801477006</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>3676.99721560962</v>
+        <v>3676.94801477006</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>0.00127009512272908</v>
+        <v>0.00125912420532825</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.0815014776941058</v>
+        <v>-0.0815113366868588</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>0.00127090203512181</v>
+        <v>0.00125991723501651</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.0005168854716</v>
+        <v>1.00052230700196</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.1132233414379</v>
+        <v>1.11446657664864</v>
       </c>
     </row>
     <row r="103">
@@ -7610,46 +7610,46 @@
         <v>3374.51907473218</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.922057940217835</v>
+        <v>0.922051433045134</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>3688.29399315392</v>
+        <v>3688.31200427301</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>3265.99372110583</v>
+        <v>3261.76531841371</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>3341.45279405164</v>
+        <v>3341.96844867294</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>3659.76900967303</v>
+        <v>3659.794837678</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>3659.76900967303</v>
+        <v>3659.794837678</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>3687.67143947789</v>
+        <v>3687.69669604853</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>3687.67143947789</v>
+        <v>3687.69669604853</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>0.00289876757331062</v>
+        <v>0.00291899727212372</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.0446238640508874</v>
+        <v>-0.0446188620887805</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>0.00290297306262954</v>
+        <v>0.00292326169292911</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.999831208228742</v>
+        <v>0.999833173488639</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.1291116133038</v>
+        <v>1.13058308494186</v>
       </c>
     </row>
     <row r="104">
@@ -7669,46 +7669,46 @@
         <v>3469.76766476378</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.924438979759211</v>
+        <v>0.924395218465592</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>3756.85171414265</v>
+        <v>3757.01766823016</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>3229.87163714881</v>
+        <v>3225.13652340521</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>3227.38764909763</v>
+        <v>3227.85392653788</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>3753.37663246043</v>
+        <v>3753.55431903171</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>3753.37663246043</v>
+        <v>3753.55431903171</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>3712.83460547591</v>
+        <v>3712.95864835464</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>3712.83460547591</v>
+        <v>3712.95864835464</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>0.00680041684150922</v>
+        <v>0.00682697659788897</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>0.00449106805447275</v>
+        <v>0.00451779161085297</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>0.00682359218032191</v>
+        <v>0.00685033352476783</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.98828351182959</v>
+        <v>0.988272873921226</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.14953008124913</v>
+        <v>1.15125627129557</v>
       </c>
     </row>
     <row r="105">
@@ -7728,46 +7728,46 @@
         <v>4016.542850834</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1.09002530662661</v>
+        <v>1.08999129768425</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>3639.85081555179</v>
+        <v>3639.91173333219</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>3196.42856931748</v>
+        <v>3191.19198551074</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>3108.49907470816</v>
+        <v>3108.85318818544</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>3684.81614730975</v>
+        <v>3684.93111767715</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>3684.81614730975</v>
+        <v>3684.93111767715</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>3560.45939336006</v>
+        <v>3560.52163049847</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>3560.45939336006</v>
+        <v>3560.52163049847</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.04190604987126</v>
+        <v>-0.0419219785914681</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.0304631253689952</v>
+        <v>-0.0304438412656398</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0410401292562604</v>
+        <v>-0.0410554041380773</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.978188275779734</v>
+        <v>0.978189003291836</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>1.11388673832318</v>
+        <v>1.11573407261758</v>
       </c>
     </row>
     <row r="106">
@@ -7787,46 +7787,46 @@
         <v>3685.04709961106</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.05350817248036</v>
+        <v>1.05363391824873</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3118.82864636032</v>
+        <v>3118.66996760788</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>3167.76809750545</v>
+        <v>3162.05071047006</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>2992.69369167566</v>
+        <v>2992.85444023288</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>3497.88183506451</v>
+        <v>3497.4643809266</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>3118.82864636032</v>
+        <v>3118.66996760788</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3083.68613200683</v>
+        <v>3083.6162834036</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3083.68613200683</v>
+        <v>3083.6162834036</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.143763902115243</v>
+        <v>-0.143804033314864</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.161357501464526</v>
+        <v>-0.161365276034113</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.133907793539893</v>
+        <v>-0.133942550161703</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>0.988732143269717</v>
+        <v>0.988760053302093</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.973457032550825</v>
+        <v>0.975195076155247</v>
       </c>
     </row>
     <row r="107">
@@ -7846,46 +7846,46 @@
         <v>1880.07334156122</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.931102172261312</v>
+        <v>0.931121769228818</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>2412.27108799693</v>
+        <v>2412.1940807215</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>3146.29904384257</v>
+        <v>3140.14029098051</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>2890.75970615557</v>
+        <v>2890.62627894493</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2019.19123117842</v>
+        <v>2019.14873402471</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>2412.27108799693</v>
+        <v>2412.1940807215</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>2470.18662933225</v>
+        <v>2470.18202209366</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>2470.18662933225</v>
+        <v>2470.18202209366</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.221831971282425</v>
+        <v>-0.22181118515619</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.33015002288762</v>
+        <v>-0.330155859959815</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.19895004757677</v>
+        <v>-0.198933396678285</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.02400872009099</v>
+        <v>1.02403950073321</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.785108660973119</v>
+        <v>0.786647026309243</v>
       </c>
     </row>
     <row r="108">
@@ -7905,46 +7905,46 @@
         <v>1803.44547006555</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.930870287442628</v>
+        <v>0.930728920778111</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>1983.87556870349</v>
+        <v>1984.1296245511</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>3134.39964330174</v>
+        <v>3127.86120677514</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>2814.11599907675</v>
+        <v>2813.56637822317</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>1937.3756949748</v>
+        <v>1937.66995932374</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>1937.3756949748</v>
+        <v>1937.66995932374</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2058.47304949502</v>
+        <v>2058.66990112741</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2058.47304949502</v>
+        <v>2058.66990112741</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.18232923638012</v>
+        <v>-0.182231745883377</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.44557911455063</v>
+        <v>-0.445544619237899</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.166673066297232</v>
+        <v>-0.166591820880252</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.03760189498189</v>
+        <v>1.03756824939962</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.656735988945764</v>
+        <v>0.658171755405325</v>
       </c>
     </row>
     <row r="109">
@@ -7964,46 +7964,46 @@
         <v>2123.17169555586</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.09055663751311</v>
+        <v>1.09040211987767</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>1880.60698461145</v>
+        <v>1880.80827655636</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>3133.98936338342</v>
+        <v>3127.15897120561</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>2771.78900827728</v>
+        <v>2770.68025097809</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1946.86972003354</v>
+        <v>1947.14560514066</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>1946.86972003354</v>
+        <v>1947.14560514066</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>1945.85861549253</v>
+        <v>1945.97223191158</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>1945.85861549253</v>
+        <v>1945.97223191158</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.0562611426243757</v>
+        <v>-0.056298380850355</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.453481025757132</v>
+        <v>-0.453458668740303</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.0547077524430634</v>
+        <v>-0.054742952793991</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.03469711184475</v>
+        <v>1.03464678253891</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.620888710800153</v>
+        <v>0.622281198311243</v>
       </c>
     </row>
     <row r="110">
@@ -8023,46 +8023,46 @@
         <v>1981.82749195669</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.03825551871355</v>
+        <v>1.03851500823098</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.663418976476775</v>
+        <v>0.662430511704517</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2038.08804764767</v>
+        <v>2037.48545379682</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>3146.2395316204</v>
+        <v>3139.23522809389</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>2768.4214700747</v>
+        <v>2766.59392802566</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>1908.80516042166</v>
+        <v>1908.32821504675</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>1952.31932692823</v>
+        <v>1951.92775804127</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2061.84781473778</v>
+        <v>2061.4755777855</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2061.84781473778</v>
+        <v>2061.4755777855</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0578992509701197</v>
+        <v>0.0576603119307608</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.331369106169065</v>
+        <v>-0.331474675081784</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0596082358305876</v>
+        <v>0.0593550843017174</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01165787077626</v>
+        <v>1.01177437804229</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.655337203037392</v>
+        <v>0.656680824468577</v>
       </c>
     </row>
     <row r="111">
@@ -8082,46 +8082,46 @@
         <v>2244.76524089118</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.936926113913071</v>
+        <v>0.937310169764165</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>2324.07756741393</v>
+        <v>2323.93636198072</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>3171.57952576834</v>
+        <v>3164.55411290819</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>2804.53152434536</v>
+        <v>2801.81576695269</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>2395.88288506115</v>
+        <v>2394.90118991879</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>2395.88288506115</v>
+        <v>2394.90118991879</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>2326.32941415729</v>
+        <v>2326.2285171013</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>2326.32941415729</v>
+        <v>2326.2285171013</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.120689088479285</v>
+        <v>0.120826267663268</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.0582373871944419</v>
+        <v>-0.0582764766745164</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.128274064423683</v>
+        <v>0.128428850755639</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.00096892064832</v>
+        <v>1.00098632439256</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.733492379824125</v>
+        <v>0.735088873219971</v>
       </c>
     </row>
     <row r="112">
@@ -8141,46 +8141,46 @@
         <v>2416.28398981369</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.943406712825488</v>
+        <v>0.942688490293977</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>2565.62030535546</v>
+        <v>2566.63943185981</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>3209.69252345501</v>
+        <v>3202.83769394793</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>2876.55680024988</v>
+        <v>2872.78079449605</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>2561.23255957864</v>
+        <v>2563.18393052638</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>2561.23255957864</v>
+        <v>2563.18393052638</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>2558.33741402334</v>
+        <v>2559.14910414587</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>2558.33741402334</v>
+        <v>2559.14910414587</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.095065933197357</v>
+        <v>0.0954265281072791</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.242832600917925</v>
+        <v>0.243108039197726</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.099731361540687</v>
+        <v>0.100127990578849</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>0.997161352630039</v>
+        <v>0.997081659534659</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.797066197253521</v>
+        <v>0.799025535693435</v>
       </c>
     </row>
     <row r="113">
@@ -8200,46 +8200,46 @@
         <v>2945.85895499108</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1.08503026248868</v>
+        <v>1.08490010902504</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>2731.96674199351</v>
+        <v>2732.67695837915</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>3259.77689190772</v>
+        <v>3253.32700643569</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>2978.89168375243</v>
+        <v>2973.88946450744</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>2715.00165187496</v>
+        <v>2715.32736561195</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>2715.00165187496</v>
+        <v>2715.32736561195</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>2763.51053350517</v>
+        <v>2763.85522730222</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>2763.51053350517</v>
+        <v>2763.85522730222</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.0771442040758122</v>
+        <v>0.0769517045201574</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.420201093492951</v>
+        <v>0.42029530636581</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.0801978340922425</v>
+        <v>0.0799899165018243</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.01154618430261</v>
+        <v>1.01140942357913</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.847760636737282</v>
+        <v>0.849547316281087</v>
       </c>
     </row>
     <row r="114">
@@ -8259,46 +8259,46 @@
         <v>3141.23369626134</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.02560639447545</v>
+        <v>1.02601643280002</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>3087.60699688758</v>
+        <v>3085.57484203374</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>3320.62571087636</v>
+        <v>3314.86330199183</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>3104.35393961385</v>
+        <v>3097.99424651871</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>3062.80627069211</v>
+        <v>3061.5822474586</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>3062.80627069211</v>
+        <v>3061.5822474586</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>3104.95708696134</v>
+        <v>3103.60156470276</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>3104.95708696134</v>
+        <v>3103.60156470276</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.116498090727893</v>
+        <v>0.115936705627144</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.50590992447045</v>
+        <v>0.505524294416695</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.123555365292237</v>
+        <v>0.122924795063221</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>1.00561926763712</v>
+        <v>1.00584225746964</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>0.935051811708674</v>
+        <v>0.936268341092036</v>
       </c>
     </row>
     <row r="115">
@@ -8318,46 +8318,46 @@
         <v>3374.61116034377</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.942835777518301</v>
+        <v>0.943705800666023</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>3563.27087167927</v>
+        <v>3562.18281662215</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>3390.69157558579</v>
+        <v>3385.95158246128</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>3244.44188243559</v>
+        <v>3236.65479956725</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>3579.21415458618</v>
+        <v>3575.91439828189</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>3579.21415458618</v>
+        <v>3575.91439828189</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>3530.56633773371</v>
+        <v>3529.73609907413</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>3530.56633773371</v>
+        <v>3529.73609907413</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.128458399029833</v>
+        <v>0.128659876486609</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.51765537427667</v>
+        <v>0.517364297241315</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.137074116920852</v>
+        <v>0.137303234802365</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.990821765977575</v>
+        <v>0.990891338480267</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.04125257606887</v>
+        <v>1.04246502441371</v>
       </c>
     </row>
     <row r="116">
@@ -8377,46 +8377,46 @@
         <v>3733.26985008941</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.956995745271982</v>
+        <v>0.955892451389662</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>3849.17242322115</v>
+        <v>3851.71406518037</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>3468.26594411076</v>
+        <v>3464.93854902985</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>3390.44608847447</v>
+        <v>3381.24872269512</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>3901.03077107036</v>
+        <v>3905.53335227414</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>3901.03077107036</v>
+        <v>3905.53335227414</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>3815.86740337451</v>
+        <v>3817.91020274167</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>3815.86740337451</v>
+        <v>3817.91020274167</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.0777097117435601</v>
+        <v>0.0784800968959416</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.491541882809555</v>
+        <v>0.491867041493041</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.0808088670057212</v>
+        <v>0.0816418269182029</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.991347485593079</v>
+        <v>0.99122368330913</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.10022341563916</v>
+        <v>1.10186952776137</v>
       </c>
     </row>
     <row r="117">
@@ -8436,46 +8436,46 @@
         <v>4166.74891556592</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1.07329747171194</v>
+        <v>1.0726161951428</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>3954.05947167177</v>
+        <v>3956.89279324498</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>3551.75810113791</v>
+        <v>3550.28962964322</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>3535.33099534809</v>
+        <v>3524.84991293798</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>3882.19391677113</v>
+        <v>3884.65970813651</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>3882.19391677113</v>
+        <v>3884.65970813651</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>3937.08032543277</v>
+        <v>3938.83356671764</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>3937.08032543277</v>
+        <v>3938.83356671764</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.0312714090152356</v>
+        <v>0.0311814248448008</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.424666299512556</v>
+        <v>0.4251229687462</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.0317654963458824</v>
+        <v>0.0316726579606657</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.995705895078048</v>
+        <v>0.995436008132905</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.10848774418827</v>
+        <v>1.10944006760189</v>
       </c>
     </row>
     <row r="118">
@@ -8495,46 +8495,46 @@
         <v>4176.79388293553</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.02299618501399</v>
+        <v>1.02360319110666</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4040.57132655491</v>
+        <v>4036.69279469611</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>3639.8478093707</v>
+        <v>3640.74562399913</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>3674.61396408701</v>
+        <v>3663.15369047938</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>4082.90269711847</v>
+        <v>4080.48149832341</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>4082.90269711847</v>
+        <v>4080.48149832341</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>4033.15377854736</v>
+        <v>4030.51590857742</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>4033.15377854736</v>
+        <v>4030.51590857742</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0241092307739148</v>
+        <v>0.0230097543596079</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.298940264096983</v>
+        <v>0.298657648074563</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0244022080255699</v>
+        <v>0.0232765209056998</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.99816423287499</v>
+        <v>0.998469815159874</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.10805560830431</v>
+        <v>1.10705781859875</v>
       </c>
     </row>
     <row r="119">
@@ -8554,46 +8554,46 @@
         <v>3855.30333176018</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.943859476026463</v>
+        <v>0.945752286960808</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>4085.141222728</v>
+        <v>4081.25002206182</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>3731.42135389738</v>
+        <v>3735.25631309436</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>3805.54667032892</v>
+        <v>3793.65442447885</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>4084.61580318137</v>
+        <v>4076.44092952634</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>4084.61580318137</v>
+        <v>4076.44092952634</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>4074.35979524872</v>
+        <v>4071.42600142236</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>4074.35979524872</v>
+        <v>4071.42600142236</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>0.010164983661921</v>
+        <v>0.0100989222076543</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.154024427101992</v>
+        <v>0.153464703066702</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>0.0102168226067987</v>
+        <v>0.0101500884186756</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.997360818906505</v>
+        <v>0.997592889289714</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.09190557935601</v>
+        <v>1.08999909514898</v>
       </c>
     </row>
     <row r="120">
@@ -8613,46 +8613,46 @@
         <v>3912.69231011997</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.967218152547455</v>
+        <v>0.965538845247007</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>4075.44206905146</v>
+        <v>4079.53630126013</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>3825.64192911104</v>
+        <v>3833.04631284716</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>3927.42223337666</v>
+        <v>3915.93312313514</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>4045.30487751366</v>
+        <v>4052.34064831334</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>4045.30487751366</v>
+        <v>4052.34064831334</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>4072.7528517631</v>
+        <v>4075.9025667901</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>4072.7528517631</v>
+        <v>4075.9025667901</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.000394481720354239</v>
+        <v>0.00109890396115723</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>0.0673203288356985</v>
+        <v>0.0675742357332456</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.00039440392267065</v>
+        <v>0.00109950797734681</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.999340140960712</v>
+        <v>0.99910927757429</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.06459332243608</v>
+        <v>1.06335854934206</v>
       </c>
     </row>
     <row r="121">
@@ -8672,46 +8672,46 @@
         <v>4375.68794227454</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>1.06314762307272</v>
+        <v>1.06141919606522</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>4075.4122208133</v>
+        <v>4081.01748024148</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>3921.89347593557</v>
+        <v>3933.55347956104</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>4040.92911819732</v>
+        <v>4030.98472717226</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>4115.78584884372</v>
+        <v>4122.48804100738</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>4115.78584884372</v>
+        <v>4122.48804100738</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>4078.32784361086</v>
+        <v>4082.03208293655</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>4078.32784361086</v>
+        <v>4082.03208293655</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>0.00136791498586075</v>
+        <v>0.00150271301820166</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.0358762093995533</v>
+        <v>0.0363555641012359</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>0.00136885100831607</v>
+        <v>0.0015038426571794</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00071541788648</v>
+        <v>1.0002486151309</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.03988745962509</v>
+        <v>1.03774668480981</v>
       </c>
     </row>
     <row r="122">
@@ -8731,46 +8731,46 @@
         <v>4139.45294223971</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.02552206293948</v>
+        <v>1.02695272108064</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>4045.71770150933</v>
+        <v>4044.23207935103</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>4019.69722463762</v>
+        <v>4036.35272849916</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>4147.3452029787</v>
+        <v>4140.48621494009</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>4036.43479924234</v>
+        <v>4030.81160141808</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>4036.43479924234</v>
+        <v>4030.81160141808</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>4071.53340520224</v>
+        <v>4067.53515226456</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>4071.53340520224</v>
+        <v>4067.53515226456</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.00166737562157574</v>
+        <v>-0.00355772166660976</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0.00951603354650632</v>
+        <v>0.00918474074456821</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.0016659863231121</v>
+        <v>-0.00355140047345182</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.00638099481911</v>
+        <v>1.00576205135025</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.01289554353669</v>
+        <v>1.0077253961343</v>
       </c>
     </row>
     <row r="123">
@@ -8790,46 +8790,46 @@
         <v>3860.80585126077</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.942239516063428</v>
+        <v>0.944879614456199</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>4157.90972556409</v>
+        <v>4134.09767985245</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>4118.69558821689</v>
+        <v>4141.13705902561</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>4248.32264956182</v>
+        <v>4246.57208135769</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>4097.47817348054</v>
+        <v>4086.02936521469</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>4097.47817348054</v>
+        <v>4086.02936521469</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>4173.39440546451</v>
+        <v>4150.50047145538</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>4173.39440546451</v>
+        <v>4150.50047145538</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.0247100242600516</v>
+        <v>0.0201917202007229</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>0.0243067905616194</v>
+        <v>0.019421811916857</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0250178471167957</v>
+        <v>0.0203969519832261</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.00372415009523</v>
+        <v>1.00396768360914</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.01328061666031</v>
+        <v>1.00226107281558</v>
       </c>
     </row>
     <row r="124">
@@ -8849,46 +8849,46 @@
         <v>4384.27601900521</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.972080436304043</v>
+        <v>0.970119579499895</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>0.613221075326813</v>
+        <v>0.242758713482659</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>4386.06503172968</v>
+        <v>4360.602762471</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>4218.54144065723</v>
+        <v>4247.59600730004</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>4344.95906776901</v>
+        <v>4350.82844827652</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>4510.19880173159</v>
+        <v>4519.31505316628</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>4462.18647565462</v>
+        <v>4399.13155397407</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>4373.69693994089</v>
+        <v>4342.64273515753</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>4373.69693994089</v>
+        <v>4342.64273515753</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.0468789223525102</v>
+        <v>0.0452541654411573</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.0738920575667905</v>
+        <v>0.0654432150907622</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.0479951126148317</v>
+        <v>0.0462937578307934</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>0.997180139441774</v>
+        <v>0.995881297083964</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.03677941806813</v>
+        <v>1.02237659318215</v>
       </c>
     </row>
     <row r="125">
@@ -8908,46 +8908,46 @@
         <v>4731.06809231028</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>1.05770961638897</v>
+        <v>1.0545640727873</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>4501.79416625325</v>
+        <v>4493.91017721966</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>4318.87439505826</v>
+        <v>4355.38466717347</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>4437.5978450422</v>
+        <v>4454.03872396732</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>4472.93663497377</v>
+        <v>4486.2784674673</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>4472.93663497377</v>
+        <v>4486.2784674673</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>4480.22939570274</v>
+        <v>4468.49429666976</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>4480.22939570274</v>
+        <v>4468.49429666976</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.0240656163674013</v>
+        <v>0.0285684175532618</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.0985456705550307</v>
+        <v>0.0946739775389518</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.024357530305539</v>
+        <v>0.0289804087481909</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.995209738661052</v>
+        <v>0.994344372818412</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.03736042910373</v>
+        <v>1.02597006651302</v>
       </c>
     </row>
     <row r="126">
@@ -8967,46 +8967,46 @@
         <v>4651.23302563202</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.03066243019718</v>
+        <v>1.0330819140797</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>4514.84957326482</v>
+        <v>4510.75786165868</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>4419.48634266649</v>
+        <v>4464.2528422136</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>4527.16850586275</v>
+        <v>4557.2278322293</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>4512.85783720881</v>
+        <v>4502.28869777037</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>4512.85783720881</v>
+        <v>4502.28869777037</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>4518.2115238725</v>
+        <v>4512.17870641207</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>4518.2115238725</v>
+        <v>4512.17870641207</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.00844198546882369</v>
+        <v>0.0097286148316063</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.109707590290072</v>
+        <v>0.10931523330535</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.00847771951279785</v>
+        <v>0.0097760916411751</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>1.00074464288414</v>
+        <v>1.00031499025152</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.02233860986353</v>
+        <v>1.01073547262944</v>
       </c>
     </row>
     <row r="127">
@@ -9026,46 +9026,46 @@
         <v>4291.63474282149</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.938227574849177</v>
+        <v>0.941590070688687</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>4573.10395089496</v>
+        <v>4562.00609131523</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>4520.26546362836</v>
+        <v>4574.0321446133</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>4614.77726866169</v>
+        <v>4661.58189557918</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>4574.19378609863</v>
+        <v>4557.85896264024</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>4574.19378609863</v>
+        <v>4557.85896264024</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>4570.6940984847</v>
+        <v>4562.84924263575</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>4570.6940984847</v>
+        <v>4562.84924263575</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>0.0115488398970322</v>
+        <v>0.0111671419812178</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.0951982138328389</v>
+        <v>0.09934916861623</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>0.0116157852138827</v>
+        <v>0.0112297272605069</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>0.9994730379112</v>
+        <v>1.00018482029696</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.01115612241407</v>
+        <v>0.997555132621724</v>
       </c>
     </row>
     <row r="128">
@@ -9085,46 +9085,46 @@
         <v>4496.73564215719</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.972996969447311</v>
+        <v>0.970506541628009</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>4595.16656357479</v>
+        <v>4591.49789616561</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>4621.15829527441</v>
+        <v>4684.57795897517</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>4701.45879852676</v>
+        <v>4768.01234086142</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>4621.53098453272</v>
+        <v>4633.39034749213</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>4621.53098453272</v>
+        <v>4633.39034749213</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>4612.88855202506</v>
+        <v>4619.36091311469</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>4612.88855202506</v>
+        <v>4619.36091311469</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0.00918916986038651</v>
+        <v>0.0123091027202341</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.054688657071746</v>
+        <v>0.0637211474287018</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>0.00923151990293003</v>
+        <v>0.012385171517588</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>1.00385665855744</v>
+        <v>1.00606839370924</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.998210460944867</v>
+        <v>0.986078351896026</v>
       </c>
     </row>
     <row r="129">
@@ -9144,46 +9144,46 @@
         <v>4901.25392352843</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>1.05760428968987</v>
+        <v>1.05339789274812</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>4706.32616004992</v>
+        <v>4744.11838093023</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>4722.14508013672</v>
+        <v>4795.73556166308</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>4788.04484313288</v>
+        <v>4876.91198025573</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>4634.29845293618</v>
+        <v>4652.80399483425</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>4634.29845293618</v>
+        <v>4652.80399483425</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>4708.10501767361</v>
+        <v>4762.38866845747</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>4708.10501767361</v>
+        <v>4762.38866845747</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>0.0204312506269245</v>
+        <v>0.0304929984472899</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>0.0508624898067573</v>
+        <v>0.0657703361077884</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>0.0206413973749151</v>
+        <v>0.030962671684023</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>1.00037797159891</v>
+        <v>1.00385114494627</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.997026761731194</v>
+        <v>0.993046552968393</v>
       </c>
     </row>
     <row r="130">
@@ -9191,92 +9191,118 @@
         <v>181</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>5208.86949768429</v>
+        <v>5294.72156588809</v>
       </c>
       <c r="C130" s="3" t="n">
-        <v>5208.86949768429</v>
+        <v>5294.72156588809</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>5208.86949768429</v>
+        <v>5294.72156588809</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5208.86949768429</v>
+        <v>5294.72156588809</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.03264433851455</v>
+        <v>1.03603623893106</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.380729905133907</v>
+        <v>1</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>4879.63588411126</v>
+        <v>5043.23153859765</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>4823.20629367817</v>
+        <v>4907.31823678372</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>4874.96751108503</v>
+        <v>4988.000515975</v>
       </c>
       <c r="K130" s="11" t="n">
-        <v>5044.20476964721</v>
+        <v>5110.55633666923</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>4942.29218028936</v>
+        <v>5110.55633666923</v>
       </c>
       <c r="M130" s="13" t="n">
-        <v>4839.62760450496</v>
+        <v>5032.8513751568</v>
       </c>
       <c r="N130" s="14" t="n">
-        <v>4839.62760450496</v>
+        <v>5032.8513751568</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>0.0275522811833358</v>
+        <v>0.0552373338102899</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>0.0711379002364587</v>
+        <v>0.115392740984488</v>
       </c>
       <c r="Q130" s="17" t="n">
-        <v>0.0279353553792099</v>
+        <v>0.0567913972437153</v>
       </c>
       <c r="R130" s="18" t="n">
-        <v>0.991800970286212</v>
+        <v>0.997941763458329</v>
       </c>
       <c r="S130" s="19" t="n">
-        <v>1.00340464616832</v>
+        <v>1.02558080244972</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
         <v>182</v>
       </c>
-      <c r="B131" s="2"/>
+      <c r="B131" s="2" t="n">
+        <v>4942.44218399254</v>
+      </c>
       <c r="C131" s="3" t="n">
-        <v>4614.83859774665</v>
+        <v>4942.44218399254</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>5600.23630467111</v>
+        <v>4942.44218399254</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3802.82797450687</v>
+        <v>4942.44218399254</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.936238958052296</v>
-      </c>
-      <c r="G131" s="7"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="10"/>
-      <c r="K131" s="11"/>
-      <c r="L131" s="12"/>
-      <c r="M131" s="13"/>
+        <v>0.940076591981105</v>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>5237.36822577607</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>5019.04993621451</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>5099.87711030502</v>
+      </c>
+      <c r="K131" s="11" t="n">
+        <v>5257.48883245449</v>
+      </c>
+      <c r="L131" s="12" t="n">
+        <v>5257.48883245449</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>5208.51133385941</v>
+      </c>
       <c r="N131" s="14" t="n">
-        <v>4929.12472617795</v>
-      </c>
-      <c r="O131" s="15"/>
-      <c r="P131" s="16"/>
-      <c r="Q131" s="17"/>
-      <c r="R131" s="18"/>
-      <c r="S131" s="19"/>
+        <v>5208.51133385941</v>
+      </c>
+      <c r="O131" s="15" t="n">
+        <v>0.0343073851833464</v>
+      </c>
+      <c r="P131" s="16" t="n">
+        <v>0.141504147275024</v>
+      </c>
+      <c r="Q131" s="17" t="n">
+        <v>0.0349026715888527</v>
+      </c>
+      <c r="R131" s="18" t="n">
+        <v>0.994490192273546</v>
+      </c>
+      <c r="S131" s="19" t="n">
+        <v>1.0377484583841</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -9284,16 +9310,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>4766.82004114845</v>
+        <v>5105.21269842935</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>6267.4831496668</v>
+        <v>6190.92129484531</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3625.47018668931</v>
+        <v>4209.9059986282</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.973228093126713</v>
+        <v>0.97032508871155</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9303,7 +9329,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>4897.9474337141</v>
+        <v>5261.34257252724</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9317,16 +9343,16 @@
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
-        <v>5469.26838078428</v>
+        <v>5857.52723387954</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>7647.29461540038</v>
+        <v>7693.83023910642</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3911.56587073383</v>
+        <v>4459.49861503903</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1.05757182340301</v>
+        <v>1.05277701403119</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
@@ -9336,7 +9362,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
       <c r="N133" s="14" t="n">
-        <v>5171.5337528429</v>
+        <v>5563.88214770236</v>
       </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
@@ -9350,16 +9376,16 @@
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="3" t="n">
-        <v>5373.61888619766</v>
+        <v>5760.97092477613</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>7913.46223802113</v>
+        <v>8045.260590788</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3648.94392183528</v>
+        <v>4125.25929043465</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>1.03368050111134</v>
+        <v>1.03737283061333</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="8"/>
@@ -9369,7 +9395,7 @@
       <c r="L134" s="12"/>
       <c r="M134" s="13"/>
       <c r="N134" s="14" t="n">
-        <v>5198.52979757316</v>
+        <v>5553.42375929592</v>
       </c>
       <c r="O134" s="15"/>
       <c r="P134" s="16"/>
@@ -9382,10 +9408,18 @@
         <v>186</v>
       </c>
       <c r="B135" s="2"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="6"/>
+      <c r="C135" s="3" t="n">
+        <v>5119.68445005018</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>7528.80551134207</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>3481.45118486574</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>0.939601684065774</v>
+      </c>
       <c r="G135" s="7"/>
       <c r="H135" s="8"/>
       <c r="I135" s="9"/>
@@ -9393,7 +9427,9 @@
       <c r="K135" s="11"/>
       <c r="L135" s="12"/>
       <c r="M135" s="13"/>
-      <c r="N135" s="14"/>
+      <c r="N135" s="14" t="n">
+        <v>5448.78168789211</v>
+      </c>
       <c r="O135" s="15"/>
       <c r="P135" s="16"/>
       <c r="Q135" s="17"/>
@@ -9868,7 +9904,7 @@
         <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0237608746453161</v>
+        <v>0.0230668508170808</v>
       </c>
     </row>
     <row r="6">
@@ -9876,7 +9912,7 @@
         <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0966850156702349</v>
+        <v>0.0956311224008344</v>
       </c>
     </row>
     <row r="7">
@@ -9884,7 +9920,7 @@
         <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.225545603442134</v>
+        <v>0.218646468330794</v>
       </c>
     </row>
     <row r="8">
@@ -9892,7 +9928,7 @@
         <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.379663141030601</v>
+        <v>0.366962606276333</v>
       </c>
     </row>
     <row r="9">
@@ -9900,7 +9936,7 @@
         <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.485729310418434</v>
+        <v>0.47639916148808</v>
       </c>
     </row>
     <row r="10">
@@ -9908,7 +9944,7 @@
         <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.477277529108288</v>
+        <v>0.47164431993063</v>
       </c>
     </row>
     <row r="11">
@@ -9916,7 +9952,7 @@
         <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.327026485568293</v>
+        <v>0.32500152109658</v>
       </c>
     </row>
     <row r="12">
@@ -9924,7 +9960,7 @@
         <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.133584057536211</v>
+        <v>0.133431531165428</v>
       </c>
     </row>
     <row r="13">
@@ -9932,7 +9968,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0168978299150181</v>
+        <v>0.0189856325747764</v>
       </c>
     </row>
     <row r="14">
